--- a/Assignments/Excel_Lookup_Functions_assignment.xlsx
+++ b/Assignments/Excel_Lookup_Functions_assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f5269e412419e72/Documents/Excel ITvedant/Assignments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{A08052DB-3A14-4E50-BB18-A04581743618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F2B2710-1B93-4989-834D-148DC5830C1A}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="13_ncr:1_{A08052DB-3A14-4E50-BB18-A04581743618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80C820B4-DE54-48B1-B4DB-B3291A98AD19}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee Dataset" sheetId="1" r:id="rId1"/>
@@ -59,8 +59,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="311">
   <si>
     <t>Employee Dataset  --  Reference table used across all lookup practice sheets</t>
   </si>
@@ -993,9 +1015,6 @@
   </si>
   <si>
     <t>IFERROR + LOOKUP</t>
-  </si>
-  <si>
-    <t>=VLOOKUP(emp_id,'Employee Dataset'!A3:L28,MATCH(emp_id,emp_id,0),FALSE)</t>
   </si>
 </sst>
 </file>
@@ -1574,6 +1593,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1668,9 +1690,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1962,36 +1981,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
     </row>
     <row r="2" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
     </row>
     <row r="3" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -3008,24 +3027,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
     </row>
     <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="80" t="s">
         <v>242</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
     </row>
     <row r="3" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
@@ -3248,44 +3267,44 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="107" t="s">
+      <c r="A15" s="108" t="s">
         <v>299</v>
       </c>
-      <c r="B15" s="107"/>
-      <c r="C15" s="107"/>
-      <c r="D15" s="107"/>
-      <c r="E15" s="107"/>
-      <c r="F15" s="107"/>
+      <c r="B15" s="108"/>
+      <c r="C15" s="108"/>
+      <c r="D15" s="108"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="108"/>
     </row>
     <row r="16" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
-      <c r="B16" s="108" t="s">
+      <c r="B16" s="109" t="s">
         <v>300</v>
       </c>
-      <c r="C16" s="108"/>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108"/>
-      <c r="F16" s="108"/>
+      <c r="C16" s="109"/>
+      <c r="D16" s="109"/>
+      <c r="E16" s="109"/>
+      <c r="F16" s="109"/>
     </row>
     <row r="17" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18"/>
-      <c r="B17" s="109" t="s">
+      <c r="B17" s="110" t="s">
         <v>301</v>
       </c>
-      <c r="C17" s="109"/>
-      <c r="D17" s="109"/>
-      <c r="E17" s="109"/>
-      <c r="F17" s="109"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="110"/>
     </row>
     <row r="18" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="44"/>
-      <c r="B18" s="106" t="s">
+      <c r="B18" s="107" t="s">
         <v>302</v>
       </c>
-      <c r="C18" s="106"/>
-      <c r="D18" s="106"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="106"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="107"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3319,26 +3338,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -3413,330 +3432,742 @@
       <c r="A6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="110" t="s">
-        <v>311</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="B6" s="78" t="str">
+        <f>VLOOKUP(A6,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Carol White</v>
+      </c>
+      <c r="C6" s="8" t="str">
+        <f>VLOOKUP(A6,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D6" s="9">
+        <f>VLOOKUP(A6,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>90000</v>
+      </c>
+      <c r="E6" s="8" t="str">
+        <f>VLOOKUP(A6,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F6" s="9">
+        <f>VLOOKUP(A6,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>18</v>
+      </c>
+      <c r="G6" s="9" t="str">
+        <f>VLOOKUP(A6,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
+      <c r="B7" s="78" t="str">
+        <f>VLOOKUP(A7,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>David Brown</v>
+      </c>
+      <c r="C7" s="8" t="str">
+        <f>VLOOKUP(A7,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="D7" s="9">
+        <f>VLOOKUP(A7,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>71000</v>
+      </c>
+      <c r="E7" s="8" t="str">
+        <f>VLOOKUP(A7,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="F7" s="9">
+        <f>VLOOKUP(A7,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="G7" s="9" t="str">
+        <f>VLOOKUP(A7,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
+      <c r="B8" s="78" t="str">
+        <f>VLOOKUP(A8,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Eva Green</v>
+      </c>
+      <c r="C8" s="8" t="str">
+        <f>VLOOKUP(A8,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D8" s="9">
+        <f>VLOOKUP(A8,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>55000</v>
+      </c>
+      <c r="E8" s="8" t="str">
+        <f>VLOOKUP(A8,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F8" s="9">
+        <f>VLOOKUP(A8,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="G8" s="9" t="str">
+        <f>VLOOKUP(A8,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
+      <c r="B9" s="78" t="str">
+        <f>VLOOKUP(A9,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Frank Lee</v>
+      </c>
+      <c r="C9" s="8" t="str">
+        <f>VLOOKUP(A9,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>HR</v>
+      </c>
+      <c r="D9" s="9">
+        <f>VLOOKUP(A9,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>68000</v>
+      </c>
+      <c r="E9" s="8" t="str">
+        <f>VLOOKUP(A9,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="F9" s="9">
+        <f>VLOOKUP(A9,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>22</v>
+      </c>
+      <c r="G9" s="9" t="str">
+        <f>VLOOKUP(A9,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>No</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="B10" s="78" t="str">
+        <f>VLOOKUP(A10,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Grace Kim</v>
+      </c>
+      <c r="C10" s="8" t="str">
+        <f>VLOOKUP(A10,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D10" s="9">
+        <f>VLOOKUP(A10,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>95000</v>
+      </c>
+      <c r="E10" s="8" t="str">
+        <f>VLOOKUP(A10,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F10" s="9">
+        <f>VLOOKUP(A10,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>14</v>
+      </c>
+      <c r="G10" s="9" t="str">
+        <f>VLOOKUP(A10,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
+      <c r="B11" s="78" t="str">
+        <f>VLOOKUP(A11,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Henry Davis</v>
+      </c>
+      <c r="C11" s="8" t="str">
+        <f>VLOOKUP(A11,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="D11" s="9">
+        <f>VLOOKUP(A11,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>58000</v>
+      </c>
+      <c r="E11" s="8" t="str">
+        <f>VLOOKUP(A11,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F11" s="9">
+        <f>VLOOKUP(A11,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G11" s="9" t="str">
+        <f>VLOOKUP(A11,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="B12" s="78" t="str">
+        <f>VLOOKUP(A12,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Isla Martin</v>
+      </c>
+      <c r="C12" s="8" t="str">
+        <f>VLOOKUP(A12,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D12" s="9">
+        <f>VLOOKUP(A12,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>72000</v>
+      </c>
+      <c r="E12" s="8" t="str">
+        <f>VLOOKUP(A12,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F12" s="9">
+        <f>VLOOKUP(A12,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>12</v>
+      </c>
+      <c r="G12" s="9" t="str">
+        <f>VLOOKUP(A12,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
+      <c r="B13" s="78" t="str">
+        <f>VLOOKUP(A13,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Jack Wilson</v>
+      </c>
+      <c r="C13" s="8" t="str">
+        <f>VLOOKUP(A13,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D13" s="9">
+        <f>VLOOKUP(A13,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>80000</v>
+      </c>
+      <c r="E13" s="8" t="str">
+        <f>VLOOKUP(A13,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="F13" s="9">
+        <f>VLOOKUP(A13,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="G13" s="9" t="str">
+        <f>VLOOKUP(A13,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="B14" s="78" t="str">
+        <f>VLOOKUP(A14,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Karen Taylor</v>
+      </c>
+      <c r="C14" s="8" t="str">
+        <f>VLOOKUP(A14,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="D14" s="9">
+        <f>VLOOKUP(A14,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>82000</v>
+      </c>
+      <c r="E14" s="8" t="str">
+        <f>VLOOKUP(A14,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F14" s="9">
+        <f>VLOOKUP(A14,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="G14" s="9" t="str">
+        <f>VLOOKUP(A14,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>No</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
+      <c r="B15" s="78" t="str">
+        <f>VLOOKUP(A15,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Liam Moore</v>
+      </c>
+      <c r="C15" s="8" t="str">
+        <f>VLOOKUP(A15,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>HR</v>
+      </c>
+      <c r="D15" s="9">
+        <f>VLOOKUP(A15,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>63000</v>
+      </c>
+      <c r="E15" s="8" t="str">
+        <f>VLOOKUP(A15,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="F15" s="9">
+        <f>VLOOKUP(A15,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>20</v>
+      </c>
+      <c r="G15" s="9" t="str">
+        <f>VLOOKUP(A15,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
+      <c r="B16" s="78" t="str">
+        <f>VLOOKUP(A16,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Mia Anderson</v>
+      </c>
+      <c r="C16" s="8" t="str">
+        <f>VLOOKUP(A16,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D16" s="9">
+        <f>VLOOKUP(A16,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>60000</v>
+      </c>
+      <c r="E16" s="8" t="str">
+        <f>VLOOKUP(A16,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F16" s="9">
+        <f>VLOOKUP(A16,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="G16" s="9" t="str">
+        <f>VLOOKUP(A16,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
+      <c r="B17" s="78" t="str">
+        <f>VLOOKUP(A17,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Noah Thomas</v>
+      </c>
+      <c r="C17" s="8" t="str">
+        <f>VLOOKUP(A17,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D17" s="9">
+        <f>VLOOKUP(A17,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>105000</v>
+      </c>
+      <c r="E17" s="8" t="str">
+        <f>VLOOKUP(A17,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F17" s="9">
+        <f>VLOOKUP(A17,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>28</v>
+      </c>
+      <c r="G17" s="9" t="str">
+        <f>VLOOKUP(A17,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="18" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
+      <c r="B18" s="78" t="str">
+        <f>VLOOKUP(A18,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Olivia Harris</v>
+      </c>
+      <c r="C18" s="8" t="str">
+        <f>VLOOKUP(A18,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="D18" s="9">
+        <f>VLOOKUP(A18,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>70000</v>
+      </c>
+      <c r="E18" s="8" t="str">
+        <f>VLOOKUP(A18,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F18" s="9">
+        <f>VLOOKUP(A18,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="G18" s="9" t="str">
+        <f>VLOOKUP(A18,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="19" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
+      <c r="B19" s="78" t="str">
+        <f>VLOOKUP(A19,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Peter Clark</v>
+      </c>
+      <c r="C19" s="8" t="str">
+        <f>VLOOKUP(A19,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>HR</v>
+      </c>
+      <c r="D19" s="9">
+        <f>VLOOKUP(A19,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>67000</v>
+      </c>
+      <c r="E19" s="8" t="str">
+        <f>VLOOKUP(A19,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F19" s="9">
+        <f>VLOOKUP(A19,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>16</v>
+      </c>
+      <c r="G19" s="9" t="str">
+        <f>VLOOKUP(A19,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>No</v>
+      </c>
     </row>
     <row r="20" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="B20" s="78" t="str">
+        <f>VLOOKUP(A20,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Quinn Lewis</v>
+      </c>
+      <c r="C20" s="8" t="str">
+        <f>VLOOKUP(A20,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D20" s="9">
+        <f>VLOOKUP(A20,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>58000</v>
+      </c>
+      <c r="E20" s="8" t="str">
+        <f>VLOOKUP(A20,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="F20" s="9">
+        <f>VLOOKUP(A20,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="G20" s="9" t="str">
+        <f>VLOOKUP(A20,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="21" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
+      <c r="B21" s="78" t="str">
+        <f>VLOOKUP(A21,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Ryan Walker</v>
+      </c>
+      <c r="C21" s="8" t="str">
+        <f>VLOOKUP(A21,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="D21" s="9">
+        <f>VLOOKUP(A21,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>88000</v>
+      </c>
+      <c r="E21" s="8" t="str">
+        <f>VLOOKUP(A21,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F21" s="9">
+        <f>VLOOKUP(A21,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>13</v>
+      </c>
+      <c r="G21" s="9" t="str">
+        <f>VLOOKUP(A21,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="22" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="B22" s="78" t="str">
+        <f>VLOOKUP(A22,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Sara Hall</v>
+      </c>
+      <c r="C22" s="8" t="str">
+        <f>VLOOKUP(A22,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D22" s="9">
+        <f>VLOOKUP(A22,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>76000</v>
+      </c>
+      <c r="E22" s="8" t="str">
+        <f>VLOOKUP(A22,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F22" s="9">
+        <f>VLOOKUP(A22,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="G22" s="9" t="str">
+        <f>VLOOKUP(A22,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="23" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
+      <c r="B23" s="78" t="str">
+        <f>VLOOKUP(A23,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Tom Young</v>
+      </c>
+      <c r="C23" s="8" t="str">
+        <f>VLOOKUP(A23,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D23" s="9">
+        <f>VLOOKUP(A23,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>65000</v>
+      </c>
+      <c r="E23" s="8" t="str">
+        <f>VLOOKUP(A23,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="F23" s="9">
+        <f>VLOOKUP(A23,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>24</v>
+      </c>
+      <c r="G23" s="9" t="str">
+        <f>VLOOKUP(A23,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="24" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="B24" s="78" t="str">
+        <f>VLOOKUP(A24,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Uma Scott</v>
+      </c>
+      <c r="C24" s="8" t="str">
+        <f>VLOOKUP(A24,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>HR</v>
+      </c>
+      <c r="D24" s="9">
+        <f>VLOOKUP(A24,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>64000</v>
+      </c>
+      <c r="E24" s="8" t="str">
+        <f>VLOOKUP(A24,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F24" s="9">
+        <f>VLOOKUP(A24,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="G24" s="9" t="str">
+        <f>VLOOKUP(A24,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="25" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
+      <c r="B25" s="78" t="str">
+        <f>VLOOKUP(A25,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Victor King</v>
+      </c>
+      <c r="C25" s="8" t="str">
+        <f>VLOOKUP(A25,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="D25" s="9">
+        <f>VLOOKUP(A25,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>79000</v>
+      </c>
+      <c r="E25" s="8" t="str">
+        <f>VLOOKUP(A25,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F25" s="9">
+        <f>VLOOKUP(A25,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="G25" s="9" t="str">
+        <f>VLOOKUP(A25,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="26" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
+      <c r="B26" s="78" t="str">
+        <f>VLOOKUP(A26,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Wendy Wright</v>
+      </c>
+      <c r="C26" s="8" t="str">
+        <f>VLOOKUP(A26,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D26" s="9">
+        <f>VLOOKUP(A26,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>87000</v>
+      </c>
+      <c r="E26" s="8" t="str">
+        <f>VLOOKUP(A26,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F26" s="9">
+        <f>VLOOKUP(A26,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="G26" s="9" t="str">
+        <f>VLOOKUP(A26,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="27" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
+      <c r="B27" s="78" t="str">
+        <f>VLOOKUP(A27,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Xander Lopez</v>
+      </c>
+      <c r="C27" s="8" t="str">
+        <f>VLOOKUP(A27,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D27" s="9">
+        <f>VLOOKUP(A27,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>61000</v>
+      </c>
+      <c r="E27" s="8" t="str">
+        <f>VLOOKUP(A27,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="F27" s="9">
+        <f>VLOOKUP(A27,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>18</v>
+      </c>
+      <c r="G27" s="9" t="str">
+        <f>VLOOKUP(A27,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>No</v>
+      </c>
     </row>
     <row r="28" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
+      <c r="B28" s="78" t="str">
+        <f>VLOOKUP(A28,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$B$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yara Hill</v>
+      </c>
+      <c r="C28" s="8" t="str">
+        <f>VLOOKUP(A28,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$C$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="D28" s="9">
+        <f>VLOOKUP(A28,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$E$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>73000</v>
+      </c>
+      <c r="E28" s="8" t="str">
+        <f>VLOOKUP(A28,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$G$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F28" s="9">
+        <f>VLOOKUP(A28,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$F$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="G28" s="9" t="str">
+        <f>VLOOKUP(A28,'Employee Dataset'!$A$3:$L$28,MATCH('Employee Dataset'!$L$3,'Employee Dataset'!$A$3:$L$3,0),FALSE)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="30" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="82" t="s">
+      <c r="A30" s="83" t="s">
         <v>85</v>
       </c>
-      <c r="B30" s="82"/>
-      <c r="C30" s="82"/>
-      <c r="D30" s="82"/>
-      <c r="E30" s="82"/>
-      <c r="F30" s="82"/>
-      <c r="G30" s="82"/>
+      <c r="B30" s="83"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
     </row>
     <row r="31" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="83" t="s">
+      <c r="A31" s="84" t="s">
         <v>86</v>
       </c>
-      <c r="B31" s="83"/>
-      <c r="C31" s="83"/>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="83"/>
+      <c r="B31" s="84"/>
+      <c r="C31" s="84"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
     </row>
     <row r="32" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="80" t="s">
+      <c r="A32" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="80"/>
-      <c r="C32" s="80"/>
-      <c r="D32" s="81" t="s">
+      <c r="B32" s="81"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="82"/>
     </row>
     <row r="33" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="80" t="s">
+      <c r="A33" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="B33" s="80"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="81" t="s">
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
+      <c r="E33" s="82"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="82"/>
     </row>
     <row r="34" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="80" t="s">
+      <c r="A34" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="80"/>
-      <c r="C34" s="80"/>
-      <c r="D34" s="81" t="s">
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
-      <c r="G34" s="81"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="82"/>
     </row>
     <row r="35" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="80" t="s">
+      <c r="A35" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="80"/>
-      <c r="C35" s="80"/>
-      <c r="D35" s="81" t="s">
+      <c r="B35" s="81"/>
+      <c r="C35" s="81"/>
+      <c r="D35" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="E35" s="81"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="81"/>
+      <c r="E35" s="82"/>
+      <c r="F35" s="82"/>
+      <c r="G35" s="82"/>
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3777,46 +4208,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="80" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
     </row>
     <row r="3" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -3941,32 +4372,32 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="86" t="s">
+      <c r="A11" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="86"/>
-      <c r="C11" s="86"/>
-      <c r="D11" s="86"/>
-      <c r="E11" s="86"/>
-      <c r="F11" s="86"/>
-      <c r="G11" s="86"/>
-      <c r="H11" s="86"/>
-      <c r="I11" s="86"/>
-      <c r="J11" s="86"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="87"/>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="87" t="s">
+      <c r="A12" s="88" t="s">
         <v>105</v>
       </c>
-      <c r="B12" s="87"/>
-      <c r="C12" s="87"/>
-      <c r="D12" s="87"/>
-      <c r="E12" s="87"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="87"/>
-      <c r="H12" s="87"/>
-      <c r="I12" s="87"/>
-      <c r="J12" s="87"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="88"/>
+      <c r="I12" s="88"/>
+      <c r="J12" s="88"/>
     </row>
     <row r="13" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -3978,15 +4409,15 @@
       <c r="C13" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="84" t="s">
+      <c r="D13" s="85" t="s">
         <v>109</v>
       </c>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="84"/>
+      <c r="E13" s="85"/>
+      <c r="F13" s="85"/>
+      <c r="G13" s="85"/>
+      <c r="H13" s="85"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="85"/>
       <c r="K13" s="76" t="s">
         <v>307</v>
       </c>
@@ -3998,16 +4429,19 @@
       <c r="B14" s="4">
         <v>2</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="85" t="s">
+      <c r="C14" s="15">
+        <f>HLOOKUP(A14,$A$4:$E$9,MATCH(A5,A4:A9,0),FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D14" s="86" t="s">
         <v>306</v>
       </c>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="85"/>
-      <c r="H14" s="85"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="85"/>
+      <c r="E14" s="86"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
       <c r="K14" s="77">
         <v>8</v>
       </c>
@@ -4019,16 +4453,19 @@
       <c r="B15" s="6">
         <v>4</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="81" t="s">
+      <c r="C15" s="15">
+        <f>HLOOKUP(A15,$A$4:$E$9,MATCH(A7,$A$4:$A$9,0),FALSE)</f>
+        <v>88833.333333333328</v>
+      </c>
+      <c r="D15" s="82" t="s">
         <v>305</v>
       </c>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="82"/>
       <c r="K15" s="77">
         <v>88833.333333333328</v>
       </c>
@@ -4040,16 +4477,19 @@
       <c r="B16" s="4">
         <v>5</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="85" t="s">
+      <c r="C16" s="15">
+        <f t="shared" ref="C16:C17" si="0">HLOOKUP(A16,$A$4:$E$9,MATCH(A8,$A$4:$A$9,0),FALSE)</f>
+        <v>105000</v>
+      </c>
+      <c r="D16" s="86" t="s">
         <v>304</v>
       </c>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85"/>
-      <c r="G16" s="85"/>
-      <c r="H16" s="85"/>
-      <c r="I16" s="85"/>
-      <c r="J16" s="85"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
+      <c r="J16" s="86"/>
       <c r="K16" s="77">
         <v>105000</v>
       </c>
@@ -4061,16 +4501,19 @@
       <c r="B17" s="6">
         <v>6</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="81" t="s">
+      <c r="C17" s="15">
+        <f t="shared" si="0"/>
+        <v>14.6</v>
+      </c>
+      <c r="D17" s="82" t="s">
         <v>303</v>
       </c>
-      <c r="E17" s="81"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="81"/>
-      <c r="H17" s="81"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="81"/>
+      <c r="E17" s="82"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="82"/>
+      <c r="H17" s="82"/>
+      <c r="I17" s="82"/>
+      <c r="J17" s="82"/>
       <c r="K17" s="77">
         <v>14.6</v>
       </c>
@@ -4111,28 +4554,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
     </row>
     <row r="2" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="90" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
     </row>
     <row r="3" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
@@ -4222,11 +4665,26 @@
       <c r="C6" s="4">
         <v>2</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
+      <c r="D6" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A3:L28,4,2)</f>
+        <v>Carol White</v>
+      </c>
+      <c r="E6" s="18">
+        <f>INDEX('Employee Dataset'!A3:L28,4,5)</f>
+        <v>90000</v>
+      </c>
+      <c r="F6" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A3:L28,4,3)</f>
+        <v>Finance</v>
+      </c>
+      <c r="G6" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A3:L28,4,7)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="H6" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A3:L28,4,2)</f>
+        <v>Carol White</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
@@ -4238,11 +4696,26 @@
       <c r="C7" s="6">
         <v>2</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
+      <c r="D7" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A4:L29,4,2)</f>
+        <v>David Brown</v>
+      </c>
+      <c r="E7" s="18">
+        <f>INDEX('Employee Dataset'!A4:L29,4,5)</f>
+        <v>71000</v>
+      </c>
+      <c r="F7" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A4:L29,4,3)</f>
+        <v>IT</v>
+      </c>
+      <c r="G7" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A4:L29,4,7)</f>
+        <v>Average</v>
+      </c>
+      <c r="H7" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A4:L29,4,2)</f>
+        <v>David Brown</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
@@ -4254,11 +4727,26 @@
       <c r="C8" s="4">
         <v>2</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
+      <c r="D8" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A5:L30,4,2)</f>
+        <v>Eva Green</v>
+      </c>
+      <c r="E8" s="18">
+        <f>INDEX('Employee Dataset'!A5:L30,4,5)</f>
+        <v>55000</v>
+      </c>
+      <c r="F8" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A5:L30,4,3)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="G8" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A5:L30,4,7)</f>
+        <v>Good</v>
+      </c>
+      <c r="H8" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A5:L30,4,2)</f>
+        <v>Eva Green</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
@@ -4270,11 +4758,26 @@
       <c r="C9" s="6">
         <v>2</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
+      <c r="D9" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A6:L31,4,2)</f>
+        <v>Frank Lee</v>
+      </c>
+      <c r="E9" s="18">
+        <f>INDEX('Employee Dataset'!A6:L31,4,5)</f>
+        <v>68000</v>
+      </c>
+      <c r="F9" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A6:L31,4,3)</f>
+        <v>HR</v>
+      </c>
+      <c r="G9" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A6:L31,4,7)</f>
+        <v>Average</v>
+      </c>
+      <c r="H9" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A6:L31,4,2)</f>
+        <v>Frank Lee</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
@@ -4286,11 +4789,26 @@
       <c r="C10" s="4">
         <v>2</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
+      <c r="D10" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A7:L32,4,2)</f>
+        <v>Grace Kim</v>
+      </c>
+      <c r="E10" s="18">
+        <f>INDEX('Employee Dataset'!A7:L32,4,5)</f>
+        <v>95000</v>
+      </c>
+      <c r="F10" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A7:L32,4,3)</f>
+        <v>Finance</v>
+      </c>
+      <c r="G10" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A7:L32,4,7)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="H10" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A7:L32,4,2)</f>
+        <v>Grace Kim</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
@@ -4302,11 +4820,26 @@
       <c r="C11" s="6">
         <v>2</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
+      <c r="D11" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A8:L33,4,2)</f>
+        <v>Henry Davis</v>
+      </c>
+      <c r="E11" s="18">
+        <f>INDEX('Employee Dataset'!A8:L33,4,5)</f>
+        <v>58000</v>
+      </c>
+      <c r="F11" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A8:L33,4,3)</f>
+        <v>IT</v>
+      </c>
+      <c r="G11" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A8:L33,4,7)</f>
+        <v>Good</v>
+      </c>
+      <c r="H11" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A8:L33,4,2)</f>
+        <v>Henry Davis</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -4318,11 +4851,26 @@
       <c r="C12" s="4">
         <v>2</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
+      <c r="D12" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A9:L34,4,2)</f>
+        <v>Isla Martin</v>
+      </c>
+      <c r="E12" s="18">
+        <f>INDEX('Employee Dataset'!A9:L34,4,5)</f>
+        <v>72000</v>
+      </c>
+      <c r="F12" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A9:L34,4,3)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="G12" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A9:L34,4,7)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="H12" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A9:L34,4,2)</f>
+        <v>Isla Martin</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
@@ -4334,11 +4882,26 @@
       <c r="C13" s="6">
         <v>2</v>
       </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
+      <c r="D13" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A10:L35,4,2)</f>
+        <v>Jack Wilson</v>
+      </c>
+      <c r="E13" s="18">
+        <f>INDEX('Employee Dataset'!A10:L35,4,5)</f>
+        <v>80000</v>
+      </c>
+      <c r="F13" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A10:L35,4,3)</f>
+        <v>Finance</v>
+      </c>
+      <c r="G13" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A10:L35,4,7)</f>
+        <v>Average</v>
+      </c>
+      <c r="H13" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A10:L35,4,2)</f>
+        <v>Jack Wilson</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
@@ -4350,11 +4913,26 @@
       <c r="C14" s="4">
         <v>2</v>
       </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
+      <c r="D14" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A11:L36,4,2)</f>
+        <v>Karen Taylor</v>
+      </c>
+      <c r="E14" s="18">
+        <f>INDEX('Employee Dataset'!A11:L36,4,5)</f>
+        <v>82000</v>
+      </c>
+      <c r="F14" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A11:L36,4,3)</f>
+        <v>IT</v>
+      </c>
+      <c r="G14" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A11:L36,4,7)</f>
+        <v>Good</v>
+      </c>
+      <c r="H14" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A11:L36,4,2)</f>
+        <v>Karen Taylor</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
@@ -4366,11 +4944,26 @@
       <c r="C15" s="6">
         <v>2</v>
       </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
+      <c r="D15" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A12:L37,4,2)</f>
+        <v>Liam Moore</v>
+      </c>
+      <c r="E15" s="18">
+        <f>INDEX('Employee Dataset'!A12:L37,4,5)</f>
+        <v>63000</v>
+      </c>
+      <c r="F15" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A12:L37,4,3)</f>
+        <v>HR</v>
+      </c>
+      <c r="G15" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A12:L37,4,7)</f>
+        <v>Average</v>
+      </c>
+      <c r="H15" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A12:L37,4,2)</f>
+        <v>Liam Moore</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
@@ -4382,11 +4975,26 @@
       <c r="C16" s="4">
         <v>2</v>
       </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
+      <c r="D16" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A13:L38,4,2)</f>
+        <v>Mia Anderson</v>
+      </c>
+      <c r="E16" s="18">
+        <f>INDEX('Employee Dataset'!A13:L38,4,5)</f>
+        <v>60000</v>
+      </c>
+      <c r="F16" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A13:L38,4,3)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="G16" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A13:L38,4,7)</f>
+        <v>Good</v>
+      </c>
+      <c r="H16" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A13:L38,4,2)</f>
+        <v>Mia Anderson</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
@@ -4398,11 +5006,26 @@
       <c r="C17" s="6">
         <v>2</v>
       </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
+      <c r="D17" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A14:L39,4,2)</f>
+        <v>Noah Thomas</v>
+      </c>
+      <c r="E17" s="18">
+        <f>INDEX('Employee Dataset'!A14:L39,4,5)</f>
+        <v>105000</v>
+      </c>
+      <c r="F17" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A14:L39,4,3)</f>
+        <v>Finance</v>
+      </c>
+      <c r="G17" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A14:L39,4,7)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="H17" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A14:L39,4,2)</f>
+        <v>Noah Thomas</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
@@ -4414,11 +5037,26 @@
       <c r="C18" s="4">
         <v>2</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
+      <c r="D18" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A15:L40,4,2)</f>
+        <v>Olivia Harris</v>
+      </c>
+      <c r="E18" s="18">
+        <f>INDEX('Employee Dataset'!A15:L40,4,5)</f>
+        <v>70000</v>
+      </c>
+      <c r="F18" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A15:L40,4,3)</f>
+        <v>IT</v>
+      </c>
+      <c r="G18" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A15:L40,4,7)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="H18" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A15:L40,4,2)</f>
+        <v>Olivia Harris</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
@@ -4430,11 +5068,26 @@
       <c r="C19" s="6">
         <v>2</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
+      <c r="D19" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A16:L41,4,2)</f>
+        <v>Peter Clark</v>
+      </c>
+      <c r="E19" s="18">
+        <f>INDEX('Employee Dataset'!A16:L41,4,5)</f>
+        <v>67000</v>
+      </c>
+      <c r="F19" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A16:L41,4,3)</f>
+        <v>HR</v>
+      </c>
+      <c r="G19" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A16:L41,4,7)</f>
+        <v>Good</v>
+      </c>
+      <c r="H19" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A16:L41,4,2)</f>
+        <v>Peter Clark</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
@@ -4446,11 +5099,26 @@
       <c r="C20" s="4">
         <v>2</v>
       </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
+      <c r="D20" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A17:L42,4,2)</f>
+        <v>Quinn Lewis</v>
+      </c>
+      <c r="E20" s="18">
+        <f>INDEX('Employee Dataset'!A17:L42,4,5)</f>
+        <v>58000</v>
+      </c>
+      <c r="F20" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A17:L42,4,3)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="G20" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A17:L42,4,7)</f>
+        <v>Average</v>
+      </c>
+      <c r="H20" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A17:L42,4,2)</f>
+        <v>Quinn Lewis</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
@@ -4462,11 +5130,26 @@
       <c r="C21" s="6">
         <v>2</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
+      <c r="D21" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A18:L43,4,2)</f>
+        <v>Ryan Walker</v>
+      </c>
+      <c r="E21" s="18">
+        <f>INDEX('Employee Dataset'!A18:L43,4,5)</f>
+        <v>88000</v>
+      </c>
+      <c r="F21" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A18:L43,4,3)</f>
+        <v>IT</v>
+      </c>
+      <c r="G21" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A18:L43,4,7)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="H21" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A18:L43,4,2)</f>
+        <v>Ryan Walker</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
@@ -4478,11 +5161,26 @@
       <c r="C22" s="4">
         <v>2</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
+      <c r="D22" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A19:L44,4,2)</f>
+        <v>Sara Hall</v>
+      </c>
+      <c r="E22" s="18">
+        <f>INDEX('Employee Dataset'!A19:L44,4,5)</f>
+        <v>76000</v>
+      </c>
+      <c r="F22" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A19:L44,4,3)</f>
+        <v>Finance</v>
+      </c>
+      <c r="G22" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A19:L44,4,7)</f>
+        <v>Good</v>
+      </c>
+      <c r="H22" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A19:L44,4,2)</f>
+        <v>Sara Hall</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
@@ -4494,11 +5192,26 @@
       <c r="C23" s="6">
         <v>2</v>
       </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
+      <c r="D23" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A20:L45,4,2)</f>
+        <v>Tom Young</v>
+      </c>
+      <c r="E23" s="18">
+        <f>INDEX('Employee Dataset'!A20:L45,4,5)</f>
+        <v>65000</v>
+      </c>
+      <c r="F23" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A20:L45,4,3)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="G23" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A20:L45,4,7)</f>
+        <v>Average</v>
+      </c>
+      <c r="H23" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A20:L45,4,2)</f>
+        <v>Tom Young</v>
+      </c>
     </row>
     <row r="24" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
@@ -4510,11 +5223,26 @@
       <c r="C24" s="4">
         <v>2</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
+      <c r="D24" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A21:L46,4,2)</f>
+        <v>Uma Scott</v>
+      </c>
+      <c r="E24" s="18">
+        <f>INDEX('Employee Dataset'!A21:L46,4,5)</f>
+        <v>64000</v>
+      </c>
+      <c r="F24" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A21:L46,4,3)</f>
+        <v>HR</v>
+      </c>
+      <c r="G24" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A21:L46,4,7)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="H24" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A21:L46,4,2)</f>
+        <v>Uma Scott</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
@@ -4526,11 +5254,26 @@
       <c r="C25" s="6">
         <v>2</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
+      <c r="D25" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A22:L47,4,2)</f>
+        <v>Victor King</v>
+      </c>
+      <c r="E25" s="18">
+        <f>INDEX('Employee Dataset'!A22:L47,4,5)</f>
+        <v>79000</v>
+      </c>
+      <c r="F25" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A22:L47,4,3)</f>
+        <v>IT</v>
+      </c>
+      <c r="G25" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A22:L47,4,7)</f>
+        <v>Good</v>
+      </c>
+      <c r="H25" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A22:L47,4,2)</f>
+        <v>Victor King</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
@@ -4542,11 +5285,26 @@
       <c r="C26" s="4">
         <v>2</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
+      <c r="D26" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A23:L48,4,2)</f>
+        <v>Wendy Wright</v>
+      </c>
+      <c r="E26" s="18">
+        <f>INDEX('Employee Dataset'!A23:L48,4,5)</f>
+        <v>87000</v>
+      </c>
+      <c r="F26" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A23:L48,4,3)</f>
+        <v>Finance</v>
+      </c>
+      <c r="G26" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A23:L48,4,7)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="H26" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A23:L48,4,2)</f>
+        <v>Wendy Wright</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
@@ -4558,11 +5316,26 @@
       <c r="C27" s="6">
         <v>2</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
+      <c r="D27" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A24:L49,4,2)</f>
+        <v>Xander Lopez</v>
+      </c>
+      <c r="E27" s="18">
+        <f>INDEX('Employee Dataset'!A24:L49,4,5)</f>
+        <v>61000</v>
+      </c>
+      <c r="F27" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A24:L49,4,3)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="G27" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A24:L49,4,7)</f>
+        <v>Average</v>
+      </c>
+      <c r="H27" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A24:L49,4,2)</f>
+        <v>Xander Lopez</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
@@ -4574,79 +5347,94 @@
       <c r="C28" s="4">
         <v>2</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
+      <c r="D28" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A25:L50,4,2)</f>
+        <v>Yara Hill</v>
+      </c>
+      <c r="E28" s="18">
+        <f>INDEX('Employee Dataset'!A25:L50,4,5)</f>
+        <v>73000</v>
+      </c>
+      <c r="F28" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A25:L50,4,3)</f>
+        <v>IT</v>
+      </c>
+      <c r="G28" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A25:L50,4,7)</f>
+        <v>Good</v>
+      </c>
+      <c r="H28" s="17" t="str">
+        <f>INDEX('Employee Dataset'!A25:L50,4,2)</f>
+        <v>Yara Hill</v>
+      </c>
     </row>
     <row r="30" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="90" t="s">
+      <c r="A30" s="91" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="90"/>
-      <c r="C30" s="90"/>
-      <c r="D30" s="90"/>
-      <c r="E30" s="90"/>
-      <c r="F30" s="90"/>
-      <c r="G30" s="90"/>
-      <c r="H30" s="90"/>
+      <c r="B30" s="91"/>
+      <c r="C30" s="91"/>
+      <c r="D30" s="91"/>
+      <c r="E30" s="91"/>
+      <c r="F30" s="91"/>
+      <c r="G30" s="91"/>
+      <c r="H30" s="91"/>
     </row>
     <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="88" t="s">
+      <c r="A31" s="89" t="s">
         <v>118</v>
       </c>
-      <c r="B31" s="88"/>
-      <c r="C31" s="81" t="s">
+      <c r="B31" s="89"/>
+      <c r="C31" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
     </row>
     <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="88" t="s">
+      <c r="A32" s="89" t="s">
         <v>120</v>
       </c>
-      <c r="B32" s="88"/>
-      <c r="C32" s="81" t="s">
+      <c r="B32" s="89"/>
+      <c r="C32" s="82" t="s">
         <v>121</v>
       </c>
-      <c r="D32" s="81"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
     </row>
     <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="88" t="s">
+      <c r="A33" s="89" t="s">
         <v>122</v>
       </c>
-      <c r="B33" s="88"/>
-      <c r="C33" s="81" t="s">
+      <c r="B33" s="89"/>
+      <c r="C33" s="82" t="s">
         <v>123</v>
       </c>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="82"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
     </row>
     <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="88" t="s">
+      <c r="A34" s="89" t="s">
         <v>124</v>
       </c>
-      <c r="B34" s="88"/>
-      <c r="C34" s="81" t="s">
+      <c r="B34" s="89"/>
+      <c r="C34" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="D34" s="81"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -4683,22 +5471,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="93" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
     </row>
     <row r="3" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
@@ -5189,57 +5977,57 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="93" t="s">
+      <c r="A30" s="94" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="93"/>
-      <c r="C30" s="93"/>
-      <c r="D30" s="93"/>
-      <c r="E30" s="93"/>
+      <c r="B30" s="94"/>
+      <c r="C30" s="94"/>
+      <c r="D30" s="94"/>
+      <c r="E30" s="94"/>
     </row>
     <row r="31" spans="1:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="B31" s="94" t="s">
+      <c r="B31" s="95" t="s">
         <v>133</v>
       </c>
-      <c r="C31" s="94"/>
-      <c r="D31" s="94"/>
-      <c r="E31" s="94"/>
+      <c r="C31" s="95"/>
+      <c r="D31" s="95"/>
+      <c r="E31" s="95"/>
     </row>
     <row r="32" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="B32" s="91" t="s">
+      <c r="B32" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="C32" s="91"/>
-      <c r="D32" s="91"/>
-      <c r="E32" s="91"/>
+      <c r="C32" s="92"/>
+      <c r="D32" s="92"/>
+      <c r="E32" s="92"/>
     </row>
     <row r="33" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="B33" s="91" t="s">
+      <c r="B33" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="C33" s="91"/>
-      <c r="D33" s="91"/>
-      <c r="E33" s="91"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
     </row>
     <row r="34" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="B34" s="91" t="s">
+      <c r="B34" s="92" t="s">
         <v>139</v>
       </c>
-      <c r="C34" s="91"/>
-      <c r="D34" s="91"/>
-      <c r="E34" s="91"/>
+      <c r="C34" s="92"/>
+      <c r="D34" s="92"/>
+      <c r="E34" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5261,7 +6049,7 @@
   <sheetPr>
     <tabColor rgb="FF6C3483"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -5273,29 +6061,29 @@
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+    <row r="1" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="79" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-    </row>
-    <row r="2" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="99" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+    </row>
+    <row r="2" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="100" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-    </row>
-    <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+    </row>
+    <row r="3" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -5318,7 +6106,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
@@ -5341,7 +6129,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>21</v>
       </c>
@@ -5364,374 +6152,792 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="26"/>
-    </row>
-    <row r="7" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="25" t="str" cm="1">
+        <f t="array" ref="B6">INDEX('Employee Dataset'!B3:B28,MATCH('Employee Dataset'!B6,'Employee Dataset'!B3:B28,0),FALSE)</f>
+        <v>Carol White</v>
+      </c>
+      <c r="C6" s="25" t="str" cm="1">
+        <f t="array" ref="C6">INDEX('Employee Dataset'!C3:C28,MATCH('Employee Dataset'!C6,'Employee Dataset'!C3:C28,0),FALSE)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D6" s="26" cm="1">
+        <f t="array" ref="D6">INDEX('Employee Dataset'!E3:E28,MATCH('Employee Dataset'!E6,'Employee Dataset'!E3:E28,0),FALSE)</f>
+        <v>90000</v>
+      </c>
+      <c r="E6" s="25" t="str" cm="1">
+        <f t="array" ref="E6">INDEX('Employee Dataset'!G3:G28,MATCH('Employee Dataset'!G6,'Employee Dataset'!G3:G28,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F6" s="25" t="str" cm="1">
+        <f t="array" ref="F6">INDEX('Employee Dataset'!H3:H28,MATCH('Employee Dataset'!H6,'Employee Dataset'!H3:H28,0),FALSE)</f>
+        <v>East</v>
+      </c>
+      <c r="G6" s="26" cm="1">
+        <f t="array" ref="G6">INDEX('Employee Dataset'!E3:E28,MATCH('Employee Dataset'!E6,'Employee Dataset'!E3:E28,0),FALSE)</f>
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="28"/>
-    </row>
-    <row r="8" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="25" t="str" cm="1">
+        <f t="array" ref="B7">INDEX('Employee Dataset'!B4:B29,MATCH('Employee Dataset'!B7,'Employee Dataset'!B4:B29,0),FALSE)</f>
+        <v>David Brown</v>
+      </c>
+      <c r="C7" s="25" t="str" cm="1">
+        <f t="array" ref="C7">INDEX('Employee Dataset'!C4:C29,MATCH('Employee Dataset'!C7,'Employee Dataset'!C4:C29,0),FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="D7" s="26" cm="1">
+        <f t="array" ref="D7">INDEX('Employee Dataset'!E4:E29,MATCH('Employee Dataset'!E7,'Employee Dataset'!E4:E29,0),FALSE)</f>
+        <v>71000</v>
+      </c>
+      <c r="E7" s="25" t="str" cm="1">
+        <f t="array" ref="E7">INDEX('Employee Dataset'!G4:G29,MATCH('Employee Dataset'!G7,'Employee Dataset'!G4:G29,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="F7" s="25" t="str" cm="1">
+        <f t="array" ref="F7">INDEX('Employee Dataset'!H4:H29,MATCH('Employee Dataset'!H7,'Employee Dataset'!H4:H29,0),FALSE)</f>
+        <v>West</v>
+      </c>
+      <c r="G7" s="26" cm="1">
+        <f t="array" ref="G7">INDEX('Employee Dataset'!E4:E29,MATCH('Employee Dataset'!E7,'Employee Dataset'!E4:E29,0),FALSE)</f>
+        <v>71000</v>
+      </c>
+      <c r="I7">
+        <f>MATCH(A6,'Employee Dataset'!A3:A28,0)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="26"/>
-    </row>
-    <row r="9" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="25" t="str" cm="1">
+        <f t="array" ref="B8">INDEX('Employee Dataset'!B5:B30,MATCH('Employee Dataset'!B8,'Employee Dataset'!B5:B30,0),FALSE)</f>
+        <v>Eva Green</v>
+      </c>
+      <c r="C8" s="25" t="str" cm="1">
+        <f t="array" ref="C8">INDEX('Employee Dataset'!C5:C30,MATCH('Employee Dataset'!C8,'Employee Dataset'!C5:C30,0),FALSE)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D8" s="26" cm="1">
+        <f t="array" ref="D8">INDEX('Employee Dataset'!E5:E30,MATCH('Employee Dataset'!E8,'Employee Dataset'!E5:E30,0),FALSE)</f>
+        <v>55000</v>
+      </c>
+      <c r="E8" s="25" t="str" cm="1">
+        <f t="array" ref="E8">INDEX('Employee Dataset'!G5:G30,MATCH('Employee Dataset'!G8,'Employee Dataset'!G5:G30,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F8" s="25" t="str" cm="1">
+        <f t="array" ref="F8">INDEX('Employee Dataset'!H5:H30,MATCH('Employee Dataset'!H8,'Employee Dataset'!H5:H30,0),FALSE)</f>
+        <v>North</v>
+      </c>
+      <c r="G8" s="26" cm="1">
+        <f t="array" ref="G8">INDEX('Employee Dataset'!E5:E30,MATCH('Employee Dataset'!E8,'Employee Dataset'!E5:E30,0),FALSE)</f>
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="28"/>
-    </row>
-    <row r="10" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="25" t="str" cm="1">
+        <f t="array" ref="B9">INDEX('Employee Dataset'!B6:B31,MATCH('Employee Dataset'!B9,'Employee Dataset'!B6:B31,0),FALSE)</f>
+        <v>Frank Lee</v>
+      </c>
+      <c r="C9" s="25" t="str" cm="1">
+        <f t="array" ref="C9">INDEX('Employee Dataset'!C6:C31,MATCH('Employee Dataset'!C9,'Employee Dataset'!C6:C31,0),FALSE)</f>
+        <v>HR</v>
+      </c>
+      <c r="D9" s="26" cm="1">
+        <f t="array" ref="D9">INDEX('Employee Dataset'!E6:E31,MATCH('Employee Dataset'!E9,'Employee Dataset'!E6:E31,0),FALSE)</f>
+        <v>68000</v>
+      </c>
+      <c r="E9" s="25" t="str" cm="1">
+        <f t="array" ref="E9">INDEX('Employee Dataset'!G6:G31,MATCH('Employee Dataset'!G9,'Employee Dataset'!G6:G31,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="F9" s="25" t="str" cm="1">
+        <f t="array" ref="F9">INDEX('Employee Dataset'!H6:H31,MATCH('Employee Dataset'!H9,'Employee Dataset'!H6:H31,0),FALSE)</f>
+        <v>South</v>
+      </c>
+      <c r="G9" s="26" cm="1">
+        <f t="array" ref="G9">INDEX('Employee Dataset'!E6:E31,MATCH('Employee Dataset'!E9,'Employee Dataset'!E6:E31,0),FALSE)</f>
+        <v>68000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="26"/>
-    </row>
-    <row r="11" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="25" t="str" cm="1">
+        <f t="array" ref="B10">INDEX('Employee Dataset'!B7:B32,MATCH('Employee Dataset'!B10,'Employee Dataset'!B7:B32,0),FALSE)</f>
+        <v>Grace Kim</v>
+      </c>
+      <c r="C10" s="25" t="str" cm="1">
+        <f t="array" ref="C10">INDEX('Employee Dataset'!C7:C32,MATCH('Employee Dataset'!C10,'Employee Dataset'!C7:C32,0),FALSE)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D10" s="26" cm="1">
+        <f t="array" ref="D10">INDEX('Employee Dataset'!E7:E32,MATCH('Employee Dataset'!E10,'Employee Dataset'!E7:E32,0),FALSE)</f>
+        <v>95000</v>
+      </c>
+      <c r="E10" s="25" t="str" cm="1">
+        <f t="array" ref="E10">INDEX('Employee Dataset'!G7:G32,MATCH('Employee Dataset'!G10,'Employee Dataset'!G7:G32,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F10" s="25" t="str" cm="1">
+        <f t="array" ref="F10">INDEX('Employee Dataset'!H7:H32,MATCH('Employee Dataset'!H10,'Employee Dataset'!H7:H32,0),FALSE)</f>
+        <v>East</v>
+      </c>
+      <c r="G10" s="26" cm="1">
+        <f t="array" ref="G10">INDEX('Employee Dataset'!E7:E32,MATCH('Employee Dataset'!E10,'Employee Dataset'!E7:E32,0),FALSE)</f>
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="28"/>
-    </row>
-    <row r="12" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="25" t="str" cm="1">
+        <f t="array" ref="B11">INDEX('Employee Dataset'!B8:B33,MATCH('Employee Dataset'!B11,'Employee Dataset'!B8:B33,0),FALSE)</f>
+        <v>Henry Davis</v>
+      </c>
+      <c r="C11" s="25" t="str" cm="1">
+        <f t="array" ref="C11">INDEX('Employee Dataset'!C8:C33,MATCH('Employee Dataset'!C11,'Employee Dataset'!C8:C33,0),FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="D11" s="26" cm="1">
+        <f t="array" ref="D11">INDEX('Employee Dataset'!E8:E33,MATCH('Employee Dataset'!E11,'Employee Dataset'!E8:E33,0),FALSE)</f>
+        <v>58000</v>
+      </c>
+      <c r="E11" s="25" t="str" cm="1">
+        <f t="array" ref="E11">INDEX('Employee Dataset'!G8:G33,MATCH('Employee Dataset'!G11,'Employee Dataset'!G8:G33,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F11" s="25" t="str" cm="1">
+        <f t="array" ref="F11">INDEX('Employee Dataset'!H8:H33,MATCH('Employee Dataset'!H11,'Employee Dataset'!H8:H33,0),FALSE)</f>
+        <v>West</v>
+      </c>
+      <c r="G11" s="26" cm="1">
+        <f t="array" ref="G11">INDEX('Employee Dataset'!E8:E33,MATCH('Employee Dataset'!E11,'Employee Dataset'!E8:E33,0),FALSE)</f>
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="26"/>
-    </row>
-    <row r="13" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="25" t="str" cm="1">
+        <f t="array" ref="B12">INDEX('Employee Dataset'!B9:B34,MATCH('Employee Dataset'!B12,'Employee Dataset'!B9:B34,0),FALSE)</f>
+        <v>Isla Martin</v>
+      </c>
+      <c r="C12" s="25" t="str" cm="1">
+        <f t="array" ref="C12">INDEX('Employee Dataset'!C9:C34,MATCH('Employee Dataset'!C12,'Employee Dataset'!C9:C34,0),FALSE)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D12" s="26" cm="1">
+        <f t="array" ref="D12">INDEX('Employee Dataset'!E9:E34,MATCH('Employee Dataset'!E12,'Employee Dataset'!E9:E34,0),FALSE)</f>
+        <v>72000</v>
+      </c>
+      <c r="E12" s="25" t="str" cm="1">
+        <f t="array" ref="E12">INDEX('Employee Dataset'!G9:G34,MATCH('Employee Dataset'!G12,'Employee Dataset'!G9:G34,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F12" s="25" t="str" cm="1">
+        <f t="array" ref="F12">INDEX('Employee Dataset'!H9:H34,MATCH('Employee Dataset'!H12,'Employee Dataset'!H9:H34,0),FALSE)</f>
+        <v>North</v>
+      </c>
+      <c r="G12" s="26" cm="1">
+        <f t="array" ref="G12">INDEX('Employee Dataset'!E9:E34,MATCH('Employee Dataset'!E12,'Employee Dataset'!E9:E34,0),FALSE)</f>
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="28"/>
-    </row>
-    <row r="14" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="25" t="str" cm="1">
+        <f t="array" ref="B13">INDEX('Employee Dataset'!B10:B35,MATCH('Employee Dataset'!B13,'Employee Dataset'!B10:B35,0),FALSE)</f>
+        <v>Jack Wilson</v>
+      </c>
+      <c r="C13" s="25" t="str" cm="1">
+        <f t="array" ref="C13">INDEX('Employee Dataset'!C10:C35,MATCH('Employee Dataset'!C13,'Employee Dataset'!C10:C35,0),FALSE)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D13" s="26" cm="1">
+        <f t="array" ref="D13">INDEX('Employee Dataset'!E10:E35,MATCH('Employee Dataset'!E13,'Employee Dataset'!E10:E35,0),FALSE)</f>
+        <v>80000</v>
+      </c>
+      <c r="E13" s="25" t="str" cm="1">
+        <f t="array" ref="E13">INDEX('Employee Dataset'!G10:G35,MATCH('Employee Dataset'!G13,'Employee Dataset'!G10:G35,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="F13" s="25" t="str" cm="1">
+        <f t="array" ref="F13">INDEX('Employee Dataset'!H10:H35,MATCH('Employee Dataset'!H13,'Employee Dataset'!H10:H35,0),FALSE)</f>
+        <v>South</v>
+      </c>
+      <c r="G13" s="26" cm="1">
+        <f t="array" ref="G13">INDEX('Employee Dataset'!E10:E35,MATCH('Employee Dataset'!E13,'Employee Dataset'!E10:E35,0),FALSE)</f>
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="26"/>
-    </row>
-    <row r="15" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="25" t="str" cm="1">
+        <f t="array" ref="B14">INDEX('Employee Dataset'!B11:B36,MATCH('Employee Dataset'!B14,'Employee Dataset'!B11:B36,0),FALSE)</f>
+        <v>Karen Taylor</v>
+      </c>
+      <c r="C14" s="25" t="str" cm="1">
+        <f t="array" ref="C14">INDEX('Employee Dataset'!C11:C36,MATCH('Employee Dataset'!C14,'Employee Dataset'!C11:C36,0),FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="D14" s="26" cm="1">
+        <f t="array" ref="D14">INDEX('Employee Dataset'!E11:E36,MATCH('Employee Dataset'!E14,'Employee Dataset'!E11:E36,0),FALSE)</f>
+        <v>82000</v>
+      </c>
+      <c r="E14" s="25" t="str" cm="1">
+        <f t="array" ref="E14">INDEX('Employee Dataset'!G11:G36,MATCH('Employee Dataset'!G14,'Employee Dataset'!G11:G36,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F14" s="25" t="str" cm="1">
+        <f t="array" ref="F14">INDEX('Employee Dataset'!H11:H36,MATCH('Employee Dataset'!H14,'Employee Dataset'!H11:H36,0),FALSE)</f>
+        <v>East</v>
+      </c>
+      <c r="G14" s="26" cm="1">
+        <f t="array" ref="G14">INDEX('Employee Dataset'!E11:E36,MATCH('Employee Dataset'!E14,'Employee Dataset'!E11:E36,0),FALSE)</f>
+        <v>82000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="28"/>
-    </row>
-    <row r="16" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="25" t="str" cm="1">
+        <f t="array" ref="B15">INDEX('Employee Dataset'!B12:B37,MATCH('Employee Dataset'!B15,'Employee Dataset'!B12:B37,0),FALSE)</f>
+        <v>Liam Moore</v>
+      </c>
+      <c r="C15" s="25" t="str" cm="1">
+        <f t="array" ref="C15">INDEX('Employee Dataset'!C12:C37,MATCH('Employee Dataset'!C15,'Employee Dataset'!C12:C37,0),FALSE)</f>
+        <v>HR</v>
+      </c>
+      <c r="D15" s="26" cm="1">
+        <f t="array" ref="D15">INDEX('Employee Dataset'!E12:E37,MATCH('Employee Dataset'!E15,'Employee Dataset'!E12:E37,0),FALSE)</f>
+        <v>63000</v>
+      </c>
+      <c r="E15" s="25" t="str" cm="1">
+        <f t="array" ref="E15">INDEX('Employee Dataset'!G12:G37,MATCH('Employee Dataset'!G15,'Employee Dataset'!G12:G37,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="F15" s="25" t="str" cm="1">
+        <f t="array" ref="F15">INDEX('Employee Dataset'!H12:H37,MATCH('Employee Dataset'!H15,'Employee Dataset'!H12:H37,0),FALSE)</f>
+        <v>West</v>
+      </c>
+      <c r="G15" s="26" cm="1">
+        <f t="array" ref="G15">INDEX('Employee Dataset'!E12:E37,MATCH('Employee Dataset'!E15,'Employee Dataset'!E12:E37,0),FALSE)</f>
+        <v>63000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="26"/>
+      <c r="B16" s="25" t="str" cm="1">
+        <f t="array" ref="B16">INDEX('Employee Dataset'!B13:B38,MATCH('Employee Dataset'!B16,'Employee Dataset'!B13:B38,0),FALSE)</f>
+        <v>Mia Anderson</v>
+      </c>
+      <c r="C16" s="25" t="str" cm="1">
+        <f t="array" ref="C16">INDEX('Employee Dataset'!C13:C38,MATCH('Employee Dataset'!C16,'Employee Dataset'!C13:C38,0),FALSE)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D16" s="26" cm="1">
+        <f t="array" ref="D16">INDEX('Employee Dataset'!E13:E38,MATCH('Employee Dataset'!E16,'Employee Dataset'!E13:E38,0),FALSE)</f>
+        <v>60000</v>
+      </c>
+      <c r="E16" s="25" t="str" cm="1">
+        <f t="array" ref="E16">INDEX('Employee Dataset'!G13:G38,MATCH('Employee Dataset'!G16,'Employee Dataset'!G13:G38,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F16" s="25" t="str" cm="1">
+        <f t="array" ref="F16">INDEX('Employee Dataset'!H13:H38,MATCH('Employee Dataset'!H16,'Employee Dataset'!H13:H38,0),FALSE)</f>
+        <v>North</v>
+      </c>
+      <c r="G16" s="26" cm="1">
+        <f t="array" ref="G16">INDEX('Employee Dataset'!E13:E38,MATCH('Employee Dataset'!E16,'Employee Dataset'!E13:E38,0),FALSE)</f>
+        <v>60000</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="28"/>
+      <c r="B17" s="25" t="str" cm="1">
+        <f t="array" ref="B17">INDEX('Employee Dataset'!B14:B39,MATCH('Employee Dataset'!B17,'Employee Dataset'!B14:B39,0),FALSE)</f>
+        <v>Noah Thomas</v>
+      </c>
+      <c r="C17" s="25" t="str" cm="1">
+        <f t="array" ref="C17">INDEX('Employee Dataset'!C14:C39,MATCH('Employee Dataset'!C17,'Employee Dataset'!C14:C39,0),FALSE)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D17" s="26" cm="1">
+        <f t="array" ref="D17">INDEX('Employee Dataset'!E14:E39,MATCH('Employee Dataset'!E17,'Employee Dataset'!E14:E39,0),FALSE)</f>
+        <v>105000</v>
+      </c>
+      <c r="E17" s="25" t="str" cm="1">
+        <f t="array" ref="E17">INDEX('Employee Dataset'!G14:G39,MATCH('Employee Dataset'!G17,'Employee Dataset'!G14:G39,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F17" s="25" t="str" cm="1">
+        <f t="array" ref="F17">INDEX('Employee Dataset'!H14:H39,MATCH('Employee Dataset'!H17,'Employee Dataset'!H14:H39,0),FALSE)</f>
+        <v>South</v>
+      </c>
+      <c r="G17" s="26" cm="1">
+        <f t="array" ref="G17">INDEX('Employee Dataset'!E14:E39,MATCH('Employee Dataset'!E17,'Employee Dataset'!E14:E39,0),FALSE)</f>
+        <v>105000</v>
+      </c>
     </row>
     <row r="18" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="26"/>
+      <c r="B18" s="25" t="str" cm="1">
+        <f t="array" ref="B18">INDEX('Employee Dataset'!B15:B40,MATCH('Employee Dataset'!B18,'Employee Dataset'!B15:B40,0),FALSE)</f>
+        <v>Olivia Harris</v>
+      </c>
+      <c r="C18" s="25" t="str" cm="1">
+        <f t="array" ref="C18">INDEX('Employee Dataset'!C15:C40,MATCH('Employee Dataset'!C18,'Employee Dataset'!C15:C40,0),FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="D18" s="26" cm="1">
+        <f t="array" ref="D18">INDEX('Employee Dataset'!E15:E40,MATCH('Employee Dataset'!E18,'Employee Dataset'!E15:E40,0),FALSE)</f>
+        <v>70000</v>
+      </c>
+      <c r="E18" s="25" t="str" cm="1">
+        <f t="array" ref="E18">INDEX('Employee Dataset'!G15:G40,MATCH('Employee Dataset'!G18,'Employee Dataset'!G15:G40,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F18" s="25" t="str" cm="1">
+        <f t="array" ref="F18">INDEX('Employee Dataset'!H15:H40,MATCH('Employee Dataset'!H18,'Employee Dataset'!H15:H40,0),FALSE)</f>
+        <v>East</v>
+      </c>
+      <c r="G18" s="26" cm="1">
+        <f t="array" ref="G18">INDEX('Employee Dataset'!E15:E40,MATCH('Employee Dataset'!E18,'Employee Dataset'!E15:E40,0),FALSE)</f>
+        <v>70000</v>
+      </c>
     </row>
     <row r="19" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="28"/>
+      <c r="B19" s="25" t="str" cm="1">
+        <f t="array" ref="B19">INDEX('Employee Dataset'!B16:B41,MATCH('Employee Dataset'!B19,'Employee Dataset'!B16:B41,0),FALSE)</f>
+        <v>Peter Clark</v>
+      </c>
+      <c r="C19" s="25" t="str" cm="1">
+        <f t="array" ref="C19">INDEX('Employee Dataset'!C16:C41,MATCH('Employee Dataset'!C19,'Employee Dataset'!C16:C41,0),FALSE)</f>
+        <v>HR</v>
+      </c>
+      <c r="D19" s="26" cm="1">
+        <f t="array" ref="D19">INDEX('Employee Dataset'!E16:E41,MATCH('Employee Dataset'!E19,'Employee Dataset'!E16:E41,0),FALSE)</f>
+        <v>67000</v>
+      </c>
+      <c r="E19" s="25" t="str" cm="1">
+        <f t="array" ref="E19">INDEX('Employee Dataset'!G16:G41,MATCH('Employee Dataset'!G19,'Employee Dataset'!G16:G41,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F19" s="25" t="str" cm="1">
+        <f t="array" ref="F19">INDEX('Employee Dataset'!H16:H41,MATCH('Employee Dataset'!H19,'Employee Dataset'!H16:H41,0),FALSE)</f>
+        <v>West</v>
+      </c>
+      <c r="G19" s="26" cm="1">
+        <f t="array" ref="G19">INDEX('Employee Dataset'!E16:E41,MATCH('Employee Dataset'!E19,'Employee Dataset'!E16:E41,0),FALSE)</f>
+        <v>67000</v>
+      </c>
     </row>
     <row r="20" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="26"/>
+      <c r="B20" s="25" t="str" cm="1">
+        <f t="array" ref="B20">INDEX('Employee Dataset'!B17:B42,MATCH('Employee Dataset'!B20,'Employee Dataset'!B17:B42,0),FALSE)</f>
+        <v>Quinn Lewis</v>
+      </c>
+      <c r="C20" s="25" t="str" cm="1">
+        <f t="array" ref="C20">INDEX('Employee Dataset'!C17:C42,MATCH('Employee Dataset'!C20,'Employee Dataset'!C17:C42,0),FALSE)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D20" s="26" cm="1">
+        <f t="array" ref="D20">INDEX('Employee Dataset'!E17:E42,MATCH('Employee Dataset'!E20,'Employee Dataset'!E17:E42,0),FALSE)</f>
+        <v>58000</v>
+      </c>
+      <c r="E20" s="25" t="str" cm="1">
+        <f t="array" ref="E20">INDEX('Employee Dataset'!G17:G42,MATCH('Employee Dataset'!G20,'Employee Dataset'!G17:G42,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="F20" s="25" t="str" cm="1">
+        <f t="array" ref="F20">INDEX('Employee Dataset'!H17:H42,MATCH('Employee Dataset'!H20,'Employee Dataset'!H17:H42,0),FALSE)</f>
+        <v>North</v>
+      </c>
+      <c r="G20" s="26" cm="1">
+        <f t="array" ref="G20">INDEX('Employee Dataset'!E17:E42,MATCH('Employee Dataset'!E20,'Employee Dataset'!E17:E42,0),FALSE)</f>
+        <v>58000</v>
+      </c>
     </row>
     <row r="21" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="28"/>
+      <c r="B21" s="25" t="str" cm="1">
+        <f t="array" ref="B21">INDEX('Employee Dataset'!B18:B43,MATCH('Employee Dataset'!B21,'Employee Dataset'!B18:B43,0),FALSE)</f>
+        <v>Ryan Walker</v>
+      </c>
+      <c r="C21" s="25" t="str" cm="1">
+        <f t="array" ref="C21">INDEX('Employee Dataset'!C18:C43,MATCH('Employee Dataset'!C21,'Employee Dataset'!C18:C43,0),FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="D21" s="26" cm="1">
+        <f t="array" ref="D21">INDEX('Employee Dataset'!E18:E43,MATCH('Employee Dataset'!E21,'Employee Dataset'!E18:E43,0),FALSE)</f>
+        <v>88000</v>
+      </c>
+      <c r="E21" s="25" t="str" cm="1">
+        <f t="array" ref="E21">INDEX('Employee Dataset'!G18:G43,MATCH('Employee Dataset'!G21,'Employee Dataset'!G18:G43,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F21" s="25" t="str" cm="1">
+        <f t="array" ref="F21">INDEX('Employee Dataset'!H18:H43,MATCH('Employee Dataset'!H21,'Employee Dataset'!H18:H43,0),FALSE)</f>
+        <v>South</v>
+      </c>
+      <c r="G21" s="26" cm="1">
+        <f t="array" ref="G21">INDEX('Employee Dataset'!E18:E43,MATCH('Employee Dataset'!E21,'Employee Dataset'!E18:E43,0),FALSE)</f>
+        <v>88000</v>
+      </c>
     </row>
     <row r="22" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="26"/>
+      <c r="B22" s="25" t="str" cm="1">
+        <f t="array" ref="B22">INDEX('Employee Dataset'!B19:B44,MATCH('Employee Dataset'!B22,'Employee Dataset'!B19:B44,0),FALSE)</f>
+        <v>Sara Hall</v>
+      </c>
+      <c r="C22" s="25" t="str" cm="1">
+        <f t="array" ref="C22">INDEX('Employee Dataset'!C19:C44,MATCH('Employee Dataset'!C22,'Employee Dataset'!C19:C44,0),FALSE)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D22" s="26" cm="1">
+        <f t="array" ref="D22">INDEX('Employee Dataset'!E19:E44,MATCH('Employee Dataset'!E22,'Employee Dataset'!E19:E44,0),FALSE)</f>
+        <v>76000</v>
+      </c>
+      <c r="E22" s="25" t="str" cm="1">
+        <f t="array" ref="E22">INDEX('Employee Dataset'!G19:G44,MATCH('Employee Dataset'!G22,'Employee Dataset'!G19:G44,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F22" s="25" t="str" cm="1">
+        <f t="array" ref="F22">INDEX('Employee Dataset'!H19:H44,MATCH('Employee Dataset'!H22,'Employee Dataset'!H19:H44,0),FALSE)</f>
+        <v>East</v>
+      </c>
+      <c r="G22" s="26" cm="1">
+        <f t="array" ref="G22">INDEX('Employee Dataset'!E19:E44,MATCH('Employee Dataset'!E22,'Employee Dataset'!E19:E44,0),FALSE)</f>
+        <v>76000</v>
+      </c>
     </row>
     <row r="23" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="28"/>
+      <c r="B23" s="25" t="str" cm="1">
+        <f t="array" ref="B23">INDEX('Employee Dataset'!B20:B45,MATCH('Employee Dataset'!B23,'Employee Dataset'!B20:B45,0),FALSE)</f>
+        <v>Tom Young</v>
+      </c>
+      <c r="C23" s="25" t="str" cm="1">
+        <f t="array" ref="C23">INDEX('Employee Dataset'!C20:C45,MATCH('Employee Dataset'!C23,'Employee Dataset'!C20:C45,0),FALSE)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D23" s="26" cm="1">
+        <f t="array" ref="D23">INDEX('Employee Dataset'!E20:E45,MATCH('Employee Dataset'!E23,'Employee Dataset'!E20:E45,0),FALSE)</f>
+        <v>65000</v>
+      </c>
+      <c r="E23" s="25" t="str" cm="1">
+        <f t="array" ref="E23">INDEX('Employee Dataset'!G20:G45,MATCH('Employee Dataset'!G23,'Employee Dataset'!G20:G45,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="F23" s="25" t="str" cm="1">
+        <f t="array" ref="F23">INDEX('Employee Dataset'!H20:H45,MATCH('Employee Dataset'!H23,'Employee Dataset'!H20:H45,0),FALSE)</f>
+        <v>West</v>
+      </c>
+      <c r="G23" s="26" cm="1">
+        <f t="array" ref="G23">INDEX('Employee Dataset'!E20:E45,MATCH('Employee Dataset'!E23,'Employee Dataset'!E20:E45,0),FALSE)</f>
+        <v>65000</v>
+      </c>
     </row>
     <row r="24" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="26"/>
+      <c r="B24" s="25" t="str" cm="1">
+        <f t="array" ref="B24">INDEX('Employee Dataset'!B21:B46,MATCH('Employee Dataset'!B24,'Employee Dataset'!B21:B46,0),FALSE)</f>
+        <v>Uma Scott</v>
+      </c>
+      <c r="C24" s="25" t="str" cm="1">
+        <f t="array" ref="C24">INDEX('Employee Dataset'!C21:C46,MATCH('Employee Dataset'!C24,'Employee Dataset'!C21:C46,0),FALSE)</f>
+        <v>HR</v>
+      </c>
+      <c r="D24" s="26" cm="1">
+        <f t="array" ref="D24">INDEX('Employee Dataset'!E21:E46,MATCH('Employee Dataset'!E24,'Employee Dataset'!E21:E46,0),FALSE)</f>
+        <v>64000</v>
+      </c>
+      <c r="E24" s="25" t="str" cm="1">
+        <f t="array" ref="E24">INDEX('Employee Dataset'!G21:G46,MATCH('Employee Dataset'!G24,'Employee Dataset'!G21:G46,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F24" s="25" t="str" cm="1">
+        <f t="array" ref="F24">INDEX('Employee Dataset'!H21:H46,MATCH('Employee Dataset'!H24,'Employee Dataset'!H21:H46,0),FALSE)</f>
+        <v>North</v>
+      </c>
+      <c r="G24" s="26" cm="1">
+        <f t="array" ref="G24">INDEX('Employee Dataset'!E21:E46,MATCH('Employee Dataset'!E24,'Employee Dataset'!E21:E46,0),FALSE)</f>
+        <v>64000</v>
+      </c>
     </row>
     <row r="25" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="28"/>
+      <c r="B25" s="25" t="str" cm="1">
+        <f t="array" ref="B25">INDEX('Employee Dataset'!B22:B47,MATCH('Employee Dataset'!B25,'Employee Dataset'!B22:B47,0),FALSE)</f>
+        <v>Victor King</v>
+      </c>
+      <c r="C25" s="25" t="str" cm="1">
+        <f t="array" ref="C25">INDEX('Employee Dataset'!C22:C47,MATCH('Employee Dataset'!C25,'Employee Dataset'!C22:C47,0),FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="D25" s="26" cm="1">
+        <f t="array" ref="D25">INDEX('Employee Dataset'!E22:E47,MATCH('Employee Dataset'!E25,'Employee Dataset'!E22:E47,0),FALSE)</f>
+        <v>79000</v>
+      </c>
+      <c r="E25" s="25" t="str" cm="1">
+        <f t="array" ref="E25">INDEX('Employee Dataset'!G22:G47,MATCH('Employee Dataset'!G25,'Employee Dataset'!G22:G47,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F25" s="25" t="str" cm="1">
+        <f t="array" ref="F25">INDEX('Employee Dataset'!H22:H47,MATCH('Employee Dataset'!H25,'Employee Dataset'!H22:H47,0),FALSE)</f>
+        <v>South</v>
+      </c>
+      <c r="G25" s="26" cm="1">
+        <f t="array" ref="G25">INDEX('Employee Dataset'!E22:E47,MATCH('Employee Dataset'!E25,'Employee Dataset'!E22:E47,0),FALSE)</f>
+        <v>79000</v>
+      </c>
     </row>
     <row r="26" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="26"/>
+      <c r="B26" s="25" t="str" cm="1">
+        <f t="array" ref="B26">INDEX('Employee Dataset'!B23:B48,MATCH('Employee Dataset'!B26,'Employee Dataset'!B23:B48,0),FALSE)</f>
+        <v>Wendy Wright</v>
+      </c>
+      <c r="C26" s="25" t="str" cm="1">
+        <f t="array" ref="C26">INDEX('Employee Dataset'!C23:C48,MATCH('Employee Dataset'!C26,'Employee Dataset'!C23:C48,0),FALSE)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D26" s="26" cm="1">
+        <f t="array" ref="D26">INDEX('Employee Dataset'!E23:E48,MATCH('Employee Dataset'!E26,'Employee Dataset'!E23:E48,0),FALSE)</f>
+        <v>87000</v>
+      </c>
+      <c r="E26" s="25" t="str" cm="1">
+        <f t="array" ref="E26">INDEX('Employee Dataset'!G23:G48,MATCH('Employee Dataset'!G26,'Employee Dataset'!G23:G48,0),FALSE)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F26" s="25" t="str" cm="1">
+        <f t="array" ref="F26">INDEX('Employee Dataset'!H23:H48,MATCH('Employee Dataset'!H26,'Employee Dataset'!H23:H48,0),FALSE)</f>
+        <v>East</v>
+      </c>
+      <c r="G26" s="26" cm="1">
+        <f t="array" ref="G26">INDEX('Employee Dataset'!E23:E48,MATCH('Employee Dataset'!E26,'Employee Dataset'!E23:E48,0),FALSE)</f>
+        <v>87000</v>
+      </c>
     </row>
     <row r="27" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="28"/>
+      <c r="B27" s="25" t="str" cm="1">
+        <f t="array" ref="B27">INDEX('Employee Dataset'!B24:B49,MATCH('Employee Dataset'!B27,'Employee Dataset'!B24:B49,0),FALSE)</f>
+        <v>Xander Lopez</v>
+      </c>
+      <c r="C27" s="25" t="str" cm="1">
+        <f t="array" ref="C27">INDEX('Employee Dataset'!C24:C49,MATCH('Employee Dataset'!C27,'Employee Dataset'!C24:C49,0),FALSE)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D27" s="26" cm="1">
+        <f t="array" ref="D27">INDEX('Employee Dataset'!E24:E49,MATCH('Employee Dataset'!E27,'Employee Dataset'!E24:E49,0),FALSE)</f>
+        <v>61000</v>
+      </c>
+      <c r="E27" s="25" t="str" cm="1">
+        <f t="array" ref="E27">INDEX('Employee Dataset'!G24:G49,MATCH('Employee Dataset'!G27,'Employee Dataset'!G24:G49,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="F27" s="25" t="str" cm="1">
+        <f t="array" ref="F27">INDEX('Employee Dataset'!H24:H49,MATCH('Employee Dataset'!H27,'Employee Dataset'!H24:H49,0),FALSE)</f>
+        <v>West</v>
+      </c>
+      <c r="G27" s="26" cm="1">
+        <f t="array" ref="G27">INDEX('Employee Dataset'!E24:E49,MATCH('Employee Dataset'!E27,'Employee Dataset'!E24:E49,0),FALSE)</f>
+        <v>61000</v>
+      </c>
     </row>
     <row r="28" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="26"/>
+      <c r="B28" s="25" t="str" cm="1">
+        <f t="array" ref="B28">INDEX('Employee Dataset'!B25:B50,MATCH('Employee Dataset'!B28,'Employee Dataset'!B25:B50,0),FALSE)</f>
+        <v>Yara Hill</v>
+      </c>
+      <c r="C28" s="25" t="str" cm="1">
+        <f t="array" ref="C28">INDEX('Employee Dataset'!C25:C50,MATCH('Employee Dataset'!C28,'Employee Dataset'!C25:C50,0),FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="D28" s="26" cm="1">
+        <f t="array" ref="D28">INDEX('Employee Dataset'!E25:E50,MATCH('Employee Dataset'!E28,'Employee Dataset'!E25:E50,0),FALSE)</f>
+        <v>73000</v>
+      </c>
+      <c r="E28" s="25" t="str" cm="1">
+        <f t="array" ref="E28">INDEX('Employee Dataset'!G25:G50,MATCH('Employee Dataset'!G28,'Employee Dataset'!G25:G50,0),FALSE)</f>
+        <v>Good</v>
+      </c>
+      <c r="F28" s="25" t="str" cm="1">
+        <f t="array" ref="F28">INDEX('Employee Dataset'!H25:H50,MATCH('Employee Dataset'!H28,'Employee Dataset'!H25:H50,0),FALSE)</f>
+        <v>North</v>
+      </c>
+      <c r="G28" s="26" cm="1">
+        <f t="array" ref="G28">INDEX('Employee Dataset'!E25:E50,MATCH('Employee Dataset'!E28,'Employee Dataset'!E25:E50,0),FALSE)</f>
+        <v>73000</v>
+      </c>
     </row>
     <row r="30" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="100" t="s">
+      <c r="A30" s="101" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="100"/>
-      <c r="C30" s="100"/>
-      <c r="D30" s="100"/>
-      <c r="E30" s="100"/>
-      <c r="F30" s="100"/>
-      <c r="G30" s="100"/>
+      <c r="B30" s="101"/>
+      <c r="C30" s="101"/>
+      <c r="D30" s="101"/>
+      <c r="E30" s="101"/>
+      <c r="F30" s="101"/>
+      <c r="G30" s="101"/>
     </row>
     <row r="31" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="101" t="s">
+      <c r="A31" s="102" t="s">
         <v>146</v>
       </c>
-      <c r="B31" s="101"/>
-      <c r="C31" s="102" t="s">
+      <c r="B31" s="102"/>
+      <c r="C31" s="103" t="s">
         <v>147</v>
       </c>
-      <c r="D31" s="102"/>
-      <c r="E31" s="103" t="s">
+      <c r="D31" s="103"/>
+      <c r="E31" s="104" t="s">
         <v>148</v>
       </c>
-      <c r="F31" s="103"/>
-      <c r="G31" s="103"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
     </row>
     <row r="32" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="95" t="s">
+      <c r="A32" s="96" t="s">
         <v>149</v>
       </c>
-      <c r="B32" s="95"/>
-      <c r="C32" s="96" t="s">
+      <c r="B32" s="96"/>
+      <c r="C32" s="97" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="96"/>
-      <c r="E32" s="97" t="s">
+      <c r="D32" s="97"/>
+      <c r="E32" s="98" t="s">
         <v>151</v>
       </c>
-      <c r="F32" s="97"/>
-      <c r="G32" s="97"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="98"/>
     </row>
     <row r="33" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="98" t="s">
+      <c r="A33" s="99" t="s">
         <v>152</v>
       </c>
-      <c r="B33" s="98"/>
-      <c r="C33" s="96" t="s">
+      <c r="B33" s="99"/>
+      <c r="C33" s="97" t="s">
         <v>153</v>
       </c>
-      <c r="D33" s="96"/>
-      <c r="E33" s="97" t="s">
+      <c r="D33" s="97"/>
+      <c r="E33" s="98" t="s">
         <v>154</v>
       </c>
-      <c r="F33" s="97"/>
-      <c r="G33" s="97"/>
+      <c r="F33" s="98"/>
+      <c r="G33" s="98"/>
     </row>
     <row r="34" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="95" t="s">
+      <c r="A34" s="96" t="s">
         <v>155</v>
       </c>
-      <c r="B34" s="95"/>
-      <c r="C34" s="96" t="s">
+      <c r="B34" s="96"/>
+      <c r="C34" s="97" t="s">
         <v>156</v>
       </c>
-      <c r="D34" s="96"/>
-      <c r="E34" s="97" t="s">
+      <c r="D34" s="97"/>
+      <c r="E34" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="F34" s="97"/>
-      <c r="G34" s="97"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="98"/>
     </row>
     <row r="35" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="98" t="s">
+      <c r="A35" s="99" t="s">
         <v>158</v>
       </c>
-      <c r="B35" s="98"/>
-      <c r="C35" s="96" t="s">
+      <c r="B35" s="99"/>
+      <c r="C35" s="97" t="s">
         <v>159</v>
       </c>
-      <c r="D35" s="96"/>
-      <c r="E35" s="97" t="s">
+      <c r="D35" s="97"/>
+      <c r="E35" s="98" t="s">
         <v>160</v>
       </c>
-      <c r="F35" s="97"/>
-      <c r="G35" s="97"/>
+      <c r="F35" s="98"/>
+      <c r="G35" s="98"/>
     </row>
     <row r="36" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="95" t="s">
+      <c r="A36" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="95"/>
-      <c r="C36" s="96" t="s">
+      <c r="B36" s="96"/>
+      <c r="C36" s="97" t="s">
         <v>161</v>
       </c>
-      <c r="D36" s="96"/>
-      <c r="E36" s="97" t="s">
+      <c r="D36" s="97"/>
+      <c r="E36" s="98" t="s">
         <v>162</v>
       </c>
-      <c r="F36" s="97"/>
-      <c r="G36" s="97"/>
+      <c r="F36" s="98"/>
+      <c r="G36" s="98"/>
     </row>
     <row r="37" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="98" t="s">
+      <c r="A37" s="99" t="s">
         <v>163</v>
       </c>
-      <c r="B37" s="98"/>
-      <c r="C37" s="96" t="s">
+      <c r="B37" s="99"/>
+      <c r="C37" s="97" t="s">
         <v>164</v>
       </c>
-      <c r="D37" s="96"/>
-      <c r="E37" s="97" t="s">
+      <c r="D37" s="97"/>
+      <c r="E37" s="98" t="s">
         <v>165</v>
       </c>
-      <c r="F37" s="97"/>
-      <c r="G37" s="97"/>
+      <c r="F37" s="98"/>
+      <c r="G37" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -5783,26 +6989,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>166</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="88" t="s">
         <v>167</v>
       </c>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -5877,265 +7083,679 @@
       <c r="A6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="15"/>
+      <c r="B6" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A6,'Employee Dataset'!A3:A28,'Employee Dataset'!B3:B28,"N/A",0)</f>
+        <v>Carol White</v>
+      </c>
+      <c r="C6" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A6,'Employee Dataset'!A3:A28,'Employee Dataset'!C3:C28,"N/A",0)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D6" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A6,'Employee Dataset'!A3:A28,'Employee Dataset'!E3:E28,"N/A",0)</f>
+        <v>90000</v>
+      </c>
+      <c r="E6" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A6,'Employee Dataset'!A3:A28,'Employee Dataset'!G3:G28,"N/A",0)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F6" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A6,'Employee Dataset'!A3:A28,'Employee Dataset'!H3:H28,"N/A",0)</f>
+        <v>East</v>
+      </c>
+      <c r="G6" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A6,'Employee Dataset'!A3:A28,'Employee Dataset'!L3:L28,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="33"/>
+      <c r="B7" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A7,'Employee Dataset'!A4:A29,'Employee Dataset'!B4:B29,"N/A",0)</f>
+        <v>David Brown</v>
+      </c>
+      <c r="C7" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A7,'Employee Dataset'!A4:A29,'Employee Dataset'!C4:C29,"N/A",0)</f>
+        <v>IT</v>
+      </c>
+      <c r="D7" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A7,'Employee Dataset'!A4:A29,'Employee Dataset'!E4:E29,"N/A",0)</f>
+        <v>71000</v>
+      </c>
+      <c r="E7" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A7,'Employee Dataset'!A4:A29,'Employee Dataset'!G4:G29,"N/A",0)</f>
+        <v>Average</v>
+      </c>
+      <c r="F7" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A7,'Employee Dataset'!A4:A29,'Employee Dataset'!H4:H29,"N/A",0)</f>
+        <v>West</v>
+      </c>
+      <c r="G7" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A7,'Employee Dataset'!A4:A29,'Employee Dataset'!L4:L29,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="15"/>
+      <c r="B8" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A8,'Employee Dataset'!A5:A30,'Employee Dataset'!B5:B30,"N/A",0)</f>
+        <v>Eva Green</v>
+      </c>
+      <c r="C8" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A8,'Employee Dataset'!A5:A30,'Employee Dataset'!C5:C30,"N/A",0)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D8" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A8,'Employee Dataset'!A5:A30,'Employee Dataset'!E5:E30,"N/A",0)</f>
+        <v>55000</v>
+      </c>
+      <c r="E8" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A8,'Employee Dataset'!A5:A30,'Employee Dataset'!G5:G30,"N/A",0)</f>
+        <v>Good</v>
+      </c>
+      <c r="F8" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A8,'Employee Dataset'!A5:A30,'Employee Dataset'!H5:H30,"N/A",0)</f>
+        <v>North</v>
+      </c>
+      <c r="G8" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A8,'Employee Dataset'!A5:A30,'Employee Dataset'!L5:L30,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="33"/>
+      <c r="B9" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A9,'Employee Dataset'!A6:A31,'Employee Dataset'!B6:B31,"N/A",0)</f>
+        <v>Frank Lee</v>
+      </c>
+      <c r="C9" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A9,'Employee Dataset'!A6:A31,'Employee Dataset'!C6:C31,"N/A",0)</f>
+        <v>HR</v>
+      </c>
+      <c r="D9" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A9,'Employee Dataset'!A6:A31,'Employee Dataset'!E6:E31,"N/A",0)</f>
+        <v>68000</v>
+      </c>
+      <c r="E9" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A9,'Employee Dataset'!A6:A31,'Employee Dataset'!G6:G31,"N/A",0)</f>
+        <v>Average</v>
+      </c>
+      <c r="F9" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A9,'Employee Dataset'!A6:A31,'Employee Dataset'!H6:H31,"N/A",0)</f>
+        <v>South</v>
+      </c>
+      <c r="G9" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A9,'Employee Dataset'!A6:A31,'Employee Dataset'!L6:L31,"N/A",0)</f>
+        <v>No</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="15"/>
+      <c r="B10" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A10,'Employee Dataset'!A7:A32,'Employee Dataset'!B7:B32,"N/A",0)</f>
+        <v>Grace Kim</v>
+      </c>
+      <c r="C10" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A10,'Employee Dataset'!A7:A32,'Employee Dataset'!C7:C32,"N/A",0)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D10" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A10,'Employee Dataset'!A7:A32,'Employee Dataset'!E7:E32,"N/A",0)</f>
+        <v>95000</v>
+      </c>
+      <c r="E10" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A10,'Employee Dataset'!A7:A32,'Employee Dataset'!G7:G32,"N/A",0)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F10" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A10,'Employee Dataset'!A7:A32,'Employee Dataset'!H7:H32,"N/A",0)</f>
+        <v>East</v>
+      </c>
+      <c r="G10" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A10,'Employee Dataset'!A7:A32,'Employee Dataset'!L7:L32,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="33"/>
+      <c r="B11" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A11,'Employee Dataset'!A8:A33,'Employee Dataset'!B8:B33,"N/A",0)</f>
+        <v>Henry Davis</v>
+      </c>
+      <c r="C11" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A11,'Employee Dataset'!A8:A33,'Employee Dataset'!C8:C33,"N/A",0)</f>
+        <v>IT</v>
+      </c>
+      <c r="D11" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A11,'Employee Dataset'!A8:A33,'Employee Dataset'!E8:E33,"N/A",0)</f>
+        <v>58000</v>
+      </c>
+      <c r="E11" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A11,'Employee Dataset'!A8:A33,'Employee Dataset'!G8:G33,"N/A",0)</f>
+        <v>Good</v>
+      </c>
+      <c r="F11" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A11,'Employee Dataset'!A8:A33,'Employee Dataset'!H8:H33,"N/A",0)</f>
+        <v>West</v>
+      </c>
+      <c r="G11" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A11,'Employee Dataset'!A8:A33,'Employee Dataset'!L8:L33,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="15"/>
+      <c r="B12" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A12,'Employee Dataset'!A9:A34,'Employee Dataset'!B9:B34,"N/A",0)</f>
+        <v>Isla Martin</v>
+      </c>
+      <c r="C12" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A12,'Employee Dataset'!A9:A34,'Employee Dataset'!C9:C34,"N/A",0)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D12" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A12,'Employee Dataset'!A9:A34,'Employee Dataset'!E9:E34,"N/A",0)</f>
+        <v>72000</v>
+      </c>
+      <c r="E12" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A12,'Employee Dataset'!A9:A34,'Employee Dataset'!G9:G34,"N/A",0)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F12" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A12,'Employee Dataset'!A9:A34,'Employee Dataset'!H9:H34,"N/A",0)</f>
+        <v>North</v>
+      </c>
+      <c r="G12" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A12,'Employee Dataset'!A9:A34,'Employee Dataset'!L9:L34,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="33"/>
+      <c r="B13" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A13,'Employee Dataset'!A10:A35,'Employee Dataset'!B10:B35,"N/A",0)</f>
+        <v>Jack Wilson</v>
+      </c>
+      <c r="C13" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A13,'Employee Dataset'!A10:A35,'Employee Dataset'!C10:C35,"N/A",0)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D13" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A13,'Employee Dataset'!A10:A35,'Employee Dataset'!E10:E35,"N/A",0)</f>
+        <v>80000</v>
+      </c>
+      <c r="E13" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A13,'Employee Dataset'!A10:A35,'Employee Dataset'!G10:G35,"N/A",0)</f>
+        <v>Average</v>
+      </c>
+      <c r="F13" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A13,'Employee Dataset'!A10:A35,'Employee Dataset'!H10:H35,"N/A",0)</f>
+        <v>South</v>
+      </c>
+      <c r="G13" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A13,'Employee Dataset'!A10:A35,'Employee Dataset'!L10:L35,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="15"/>
+      <c r="B14" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A14,'Employee Dataset'!A11:A36,'Employee Dataset'!B11:B36,"N/A",0)</f>
+        <v>Karen Taylor</v>
+      </c>
+      <c r="C14" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A14,'Employee Dataset'!A11:A36,'Employee Dataset'!C11:C36,"N/A",0)</f>
+        <v>IT</v>
+      </c>
+      <c r="D14" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A14,'Employee Dataset'!A11:A36,'Employee Dataset'!E11:E36,"N/A",0)</f>
+        <v>82000</v>
+      </c>
+      <c r="E14" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A14,'Employee Dataset'!A11:A36,'Employee Dataset'!G11:G36,"N/A",0)</f>
+        <v>Good</v>
+      </c>
+      <c r="F14" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A14,'Employee Dataset'!A11:A36,'Employee Dataset'!H11:H36,"N/A",0)</f>
+        <v>East</v>
+      </c>
+      <c r="G14" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A14,'Employee Dataset'!A11:A36,'Employee Dataset'!L11:L36,"N/A",0)</f>
+        <v>No</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="33"/>
+      <c r="B15" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A15,'Employee Dataset'!A12:A37,'Employee Dataset'!B12:B37,"N/A",0)</f>
+        <v>Liam Moore</v>
+      </c>
+      <c r="C15" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A15,'Employee Dataset'!A12:A37,'Employee Dataset'!C12:C37,"N/A",0)</f>
+        <v>HR</v>
+      </c>
+      <c r="D15" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A15,'Employee Dataset'!A12:A37,'Employee Dataset'!E12:E37,"N/A",0)</f>
+        <v>63000</v>
+      </c>
+      <c r="E15" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A15,'Employee Dataset'!A12:A37,'Employee Dataset'!G12:G37,"N/A",0)</f>
+        <v>Average</v>
+      </c>
+      <c r="F15" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A15,'Employee Dataset'!A12:A37,'Employee Dataset'!H12:H37,"N/A",0)</f>
+        <v>West</v>
+      </c>
+      <c r="G15" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A15,'Employee Dataset'!A12:A37,'Employee Dataset'!L12:L37,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="15"/>
+      <c r="B16" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A16,'Employee Dataset'!A13:A38,'Employee Dataset'!B13:B38,"N/A",0)</f>
+        <v>Mia Anderson</v>
+      </c>
+      <c r="C16" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A16,'Employee Dataset'!A13:A38,'Employee Dataset'!C13:C38,"N/A",0)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D16" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A16,'Employee Dataset'!A13:A38,'Employee Dataset'!E13:E38,"N/A",0)</f>
+        <v>60000</v>
+      </c>
+      <c r="E16" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A16,'Employee Dataset'!A13:A38,'Employee Dataset'!G13:G38,"N/A",0)</f>
+        <v>Good</v>
+      </c>
+      <c r="F16" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A16,'Employee Dataset'!A13:A38,'Employee Dataset'!H13:H38,"N/A",0)</f>
+        <v>North</v>
+      </c>
+      <c r="G16" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A16,'Employee Dataset'!A13:A38,'Employee Dataset'!L13:L38,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="33"/>
+      <c r="B17" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A17,'Employee Dataset'!A14:A39,'Employee Dataset'!B14:B39,"N/A",0)</f>
+        <v>Noah Thomas</v>
+      </c>
+      <c r="C17" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A17,'Employee Dataset'!A14:A39,'Employee Dataset'!C14:C39,"N/A",0)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D17" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A17,'Employee Dataset'!A14:A39,'Employee Dataset'!E14:E39,"N/A",0)</f>
+        <v>105000</v>
+      </c>
+      <c r="E17" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A17,'Employee Dataset'!A14:A39,'Employee Dataset'!G14:G39,"N/A",0)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F17" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A17,'Employee Dataset'!A14:A39,'Employee Dataset'!H14:H39,"N/A",0)</f>
+        <v>South</v>
+      </c>
+      <c r="G17" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A17,'Employee Dataset'!A14:A39,'Employee Dataset'!L14:L39,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="18" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="15"/>
+      <c r="B18" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A18,'Employee Dataset'!A15:A40,'Employee Dataset'!B15:B40,"N/A",0)</f>
+        <v>Olivia Harris</v>
+      </c>
+      <c r="C18" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A18,'Employee Dataset'!A15:A40,'Employee Dataset'!C15:C40,"N/A",0)</f>
+        <v>IT</v>
+      </c>
+      <c r="D18" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A18,'Employee Dataset'!A15:A40,'Employee Dataset'!E15:E40,"N/A",0)</f>
+        <v>70000</v>
+      </c>
+      <c r="E18" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A18,'Employee Dataset'!A15:A40,'Employee Dataset'!G15:G40,"N/A",0)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F18" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A18,'Employee Dataset'!A15:A40,'Employee Dataset'!H15:H40,"N/A",0)</f>
+        <v>East</v>
+      </c>
+      <c r="G18" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A18,'Employee Dataset'!A15:A40,'Employee Dataset'!L15:L40,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="19" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="33"/>
+      <c r="B19" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A19,'Employee Dataset'!A16:A41,'Employee Dataset'!B16:B41,"N/A",0)</f>
+        <v>Peter Clark</v>
+      </c>
+      <c r="C19" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A19,'Employee Dataset'!A16:A41,'Employee Dataset'!C16:C41,"N/A",0)</f>
+        <v>HR</v>
+      </c>
+      <c r="D19" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A19,'Employee Dataset'!A16:A41,'Employee Dataset'!E16:E41,"N/A",0)</f>
+        <v>67000</v>
+      </c>
+      <c r="E19" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A19,'Employee Dataset'!A16:A41,'Employee Dataset'!G16:G41,"N/A",0)</f>
+        <v>Good</v>
+      </c>
+      <c r="F19" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A19,'Employee Dataset'!A16:A41,'Employee Dataset'!H16:H41,"N/A",0)</f>
+        <v>West</v>
+      </c>
+      <c r="G19" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A19,'Employee Dataset'!A16:A41,'Employee Dataset'!L16:L41,"N/A",0)</f>
+        <v>No</v>
+      </c>
     </row>
     <row r="20" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="15"/>
+      <c r="B20" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A20,'Employee Dataset'!A17:A42,'Employee Dataset'!B17:B42,"N/A",0)</f>
+        <v>Quinn Lewis</v>
+      </c>
+      <c r="C20" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A20,'Employee Dataset'!A17:A42,'Employee Dataset'!C17:C42,"N/A",0)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D20" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A20,'Employee Dataset'!A17:A42,'Employee Dataset'!E17:E42,"N/A",0)</f>
+        <v>58000</v>
+      </c>
+      <c r="E20" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A20,'Employee Dataset'!A17:A42,'Employee Dataset'!G17:G42,"N/A",0)</f>
+        <v>Average</v>
+      </c>
+      <c r="F20" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A20,'Employee Dataset'!A17:A42,'Employee Dataset'!H17:H42,"N/A",0)</f>
+        <v>North</v>
+      </c>
+      <c r="G20" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A20,'Employee Dataset'!A17:A42,'Employee Dataset'!L17:L42,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="21" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="33"/>
+      <c r="B21" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A21,'Employee Dataset'!A18:A43,'Employee Dataset'!B18:B43,"N/A",0)</f>
+        <v>Ryan Walker</v>
+      </c>
+      <c r="C21" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A21,'Employee Dataset'!A18:A43,'Employee Dataset'!C18:C43,"N/A",0)</f>
+        <v>IT</v>
+      </c>
+      <c r="D21" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A21,'Employee Dataset'!A18:A43,'Employee Dataset'!E18:E43,"N/A",0)</f>
+        <v>88000</v>
+      </c>
+      <c r="E21" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A21,'Employee Dataset'!A18:A43,'Employee Dataset'!G18:G43,"N/A",0)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F21" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A21,'Employee Dataset'!A18:A43,'Employee Dataset'!H18:H43,"N/A",0)</f>
+        <v>South</v>
+      </c>
+      <c r="G21" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A21,'Employee Dataset'!A18:A43,'Employee Dataset'!L18:L43,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="22" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="15"/>
+      <c r="B22" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A22,'Employee Dataset'!A19:A44,'Employee Dataset'!B19:B44,"N/A",0)</f>
+        <v>Sara Hall</v>
+      </c>
+      <c r="C22" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A22,'Employee Dataset'!A19:A44,'Employee Dataset'!C19:C44,"N/A",0)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D22" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A22,'Employee Dataset'!A19:A44,'Employee Dataset'!E19:E44,"N/A",0)</f>
+        <v>76000</v>
+      </c>
+      <c r="E22" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A22,'Employee Dataset'!A19:A44,'Employee Dataset'!G19:G44,"N/A",0)</f>
+        <v>Good</v>
+      </c>
+      <c r="F22" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A22,'Employee Dataset'!A19:A44,'Employee Dataset'!H19:H44,"N/A",0)</f>
+        <v>East</v>
+      </c>
+      <c r="G22" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A22,'Employee Dataset'!A19:A44,'Employee Dataset'!L19:L44,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="23" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="33"/>
+      <c r="B23" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A23,'Employee Dataset'!A20:A45,'Employee Dataset'!B20:B45,"N/A",0)</f>
+        <v>Tom Young</v>
+      </c>
+      <c r="C23" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A23,'Employee Dataset'!A20:A45,'Employee Dataset'!C20:C45,"N/A",0)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D23" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A23,'Employee Dataset'!A20:A45,'Employee Dataset'!E20:E45,"N/A",0)</f>
+        <v>65000</v>
+      </c>
+      <c r="E23" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A23,'Employee Dataset'!A20:A45,'Employee Dataset'!G20:G45,"N/A",0)</f>
+        <v>Average</v>
+      </c>
+      <c r="F23" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A23,'Employee Dataset'!A20:A45,'Employee Dataset'!H20:H45,"N/A",0)</f>
+        <v>West</v>
+      </c>
+      <c r="G23" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A23,'Employee Dataset'!A20:A45,'Employee Dataset'!L20:L45,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="24" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="15"/>
+      <c r="B24" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A24,'Employee Dataset'!A21:A46,'Employee Dataset'!B21:B46,"N/A",0)</f>
+        <v>Uma Scott</v>
+      </c>
+      <c r="C24" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A24,'Employee Dataset'!A21:A46,'Employee Dataset'!C21:C46,"N/A",0)</f>
+        <v>HR</v>
+      </c>
+      <c r="D24" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A24,'Employee Dataset'!A21:A46,'Employee Dataset'!E21:E46,"N/A",0)</f>
+        <v>64000</v>
+      </c>
+      <c r="E24" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A24,'Employee Dataset'!A21:A46,'Employee Dataset'!G21:G46,"N/A",0)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F24" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A24,'Employee Dataset'!A21:A46,'Employee Dataset'!H21:H46,"N/A",0)</f>
+        <v>North</v>
+      </c>
+      <c r="G24" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A24,'Employee Dataset'!A21:A46,'Employee Dataset'!L21:L46,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="25" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="33"/>
+      <c r="B25" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A25,'Employee Dataset'!A22:A47,'Employee Dataset'!B22:B47,"N/A",0)</f>
+        <v>Victor King</v>
+      </c>
+      <c r="C25" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A25,'Employee Dataset'!A22:A47,'Employee Dataset'!C22:C47,"N/A",0)</f>
+        <v>IT</v>
+      </c>
+      <c r="D25" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A25,'Employee Dataset'!A22:A47,'Employee Dataset'!E22:E47,"N/A",0)</f>
+        <v>79000</v>
+      </c>
+      <c r="E25" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A25,'Employee Dataset'!A22:A47,'Employee Dataset'!G22:G47,"N/A",0)</f>
+        <v>Good</v>
+      </c>
+      <c r="F25" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A25,'Employee Dataset'!A22:A47,'Employee Dataset'!H22:H47,"N/A",0)</f>
+        <v>South</v>
+      </c>
+      <c r="G25" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A25,'Employee Dataset'!A22:A47,'Employee Dataset'!L22:L47,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="26" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="15"/>
+      <c r="B26" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A26,'Employee Dataset'!A23:A48,'Employee Dataset'!B23:B48,"N/A",0)</f>
+        <v>Wendy Wright</v>
+      </c>
+      <c r="C26" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A26,'Employee Dataset'!A23:A48,'Employee Dataset'!C23:C48,"N/A",0)</f>
+        <v>Finance</v>
+      </c>
+      <c r="D26" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A26,'Employee Dataset'!A23:A48,'Employee Dataset'!E23:E48,"N/A",0)</f>
+        <v>87000</v>
+      </c>
+      <c r="E26" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A26,'Employee Dataset'!A23:A48,'Employee Dataset'!G23:G48,"N/A",0)</f>
+        <v>Excellent</v>
+      </c>
+      <c r="F26" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A26,'Employee Dataset'!A23:A48,'Employee Dataset'!H23:H48,"N/A",0)</f>
+        <v>East</v>
+      </c>
+      <c r="G26" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A26,'Employee Dataset'!A23:A48,'Employee Dataset'!L23:L48,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="27" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="33"/>
+      <c r="B27" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A27,'Employee Dataset'!A24:A49,'Employee Dataset'!B24:B49,"N/A",0)</f>
+        <v>Xander Lopez</v>
+      </c>
+      <c r="C27" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A27,'Employee Dataset'!A24:A49,'Employee Dataset'!C24:C49,"N/A",0)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D27" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A27,'Employee Dataset'!A24:A49,'Employee Dataset'!E24:E49,"N/A",0)</f>
+        <v>61000</v>
+      </c>
+      <c r="E27" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A27,'Employee Dataset'!A24:A49,'Employee Dataset'!G24:G49,"N/A",0)</f>
+        <v>Average</v>
+      </c>
+      <c r="F27" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A27,'Employee Dataset'!A24:A49,'Employee Dataset'!H24:H49,"N/A",0)</f>
+        <v>West</v>
+      </c>
+      <c r="G27" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A27,'Employee Dataset'!A24:A49,'Employee Dataset'!L24:L49,"N/A",0)</f>
+        <v>No</v>
+      </c>
     </row>
     <row r="28" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="15"/>
+      <c r="B28" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A28,'Employee Dataset'!A25:A50,'Employee Dataset'!B25:B50,"N/A",0)</f>
+        <v>Yara Hill</v>
+      </c>
+      <c r="C28" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A28,'Employee Dataset'!A25:A50,'Employee Dataset'!C25:C50,"N/A",0)</f>
+        <v>IT</v>
+      </c>
+      <c r="D28" s="15">
+        <f>_xlfn.XLOOKUP(XLOOKUP!A28,'Employee Dataset'!A25:A50,'Employee Dataset'!E25:E50,"N/A",0)</f>
+        <v>73000</v>
+      </c>
+      <c r="E28" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A28,'Employee Dataset'!A25:A50,'Employee Dataset'!G25:G50,"N/A",0)</f>
+        <v>Good</v>
+      </c>
+      <c r="F28" s="31" t="str">
+        <f>_xlfn.XLOOKUP(A28,'Employee Dataset'!A25:A50,'Employee Dataset'!H25:H50,"N/A",0)</f>
+        <v>North</v>
+      </c>
+      <c r="G28" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A28,'Employee Dataset'!A25:A50,'Employee Dataset'!L25:L50,"N/A",0)</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="30" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="86" t="s">
+      <c r="A30" s="87" t="s">
         <v>170</v>
       </c>
-      <c r="B30" s="86"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="86"/>
-      <c r="G30" s="86"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="87"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="87"/>
     </row>
     <row r="31" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
@@ -6144,13 +7764,13 @@
       <c r="B31" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C31" s="104" t="s">
+      <c r="C31" s="105" t="s">
         <v>173</v>
       </c>
-      <c r="D31" s="104"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="104"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="105"/>
+      <c r="G31" s="105"/>
     </row>
     <row r="32" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="34" t="s">
@@ -6159,13 +7779,13 @@
       <c r="B32" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="C32" s="91" t="s">
+      <c r="C32" s="92" t="s">
         <v>176</v>
       </c>
-      <c r="D32" s="91"/>
-      <c r="E32" s="91"/>
-      <c r="F32" s="91"/>
-      <c r="G32" s="91"/>
+      <c r="D32" s="92"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="92"/>
     </row>
     <row r="33" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="36" t="s">
@@ -6174,13 +7794,13 @@
       <c r="B33" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="C33" s="91" t="s">
+      <c r="C33" s="92" t="s">
         <v>179</v>
       </c>
-      <c r="D33" s="91"/>
-      <c r="E33" s="91"/>
-      <c r="F33" s="91"/>
-      <c r="G33" s="91"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
     </row>
     <row r="34" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="34" t="s">
@@ -6189,13 +7809,13 @@
       <c r="B34" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>182</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="91"/>
-      <c r="G34" s="91"/>
+      <c r="D34" s="92"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="92"/>
+      <c r="G34" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6220,40 +7840,41 @@
   <dimension ref="A1:E38"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="1" max="1" width="47.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="78" t="s">
+    <row r="1" spans="1:5" ht="31.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="79" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-    </row>
-    <row r="2" spans="1:5" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="79" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+    </row>
+    <row r="2" spans="1:5" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="80" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-    </row>
-    <row r="3" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="105" t="s">
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="106" t="s">
         <v>185</v>
       </c>
-      <c r="B3" s="105"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-    </row>
-    <row r="4" spans="1:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="106"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+    </row>
+    <row r="4" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="38" t="s">
         <v>186</v>
       </c>
@@ -6270,7 +7891,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>50000</v>
       </c>
@@ -6278,7 +7899,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>60000</v>
       </c>
@@ -6286,7 +7907,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>70000</v>
       </c>
@@ -6294,7 +7915,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>80000</v>
       </c>
@@ -6302,7 +7923,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>90000</v>
       </c>
@@ -6310,7 +7931,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>100000</v>
       </c>
@@ -6318,16 +7939,16 @@
         <v>194</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="105" t="s">
+    <row r="12" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="106" t="s">
         <v>195</v>
       </c>
-      <c r="B12" s="105"/>
-      <c r="C12" s="105"/>
-      <c r="D12" s="105"/>
-      <c r="E12" s="105"/>
-    </row>
-    <row r="13" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="106"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="106"/>
+      <c r="E12" s="106"/>
+    </row>
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="38" t="s">
         <v>2</v>
       </c>
@@ -6344,7 +7965,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
@@ -6363,7 +7984,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>21</v>
       </c>
@@ -6382,7 +8003,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>27</v>
       </c>
@@ -6394,10 +8015,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A16,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>90000</v>
       </c>
-      <c r="D16" s="40"/>
-      <c r="E16" s="41"/>
-    </row>
-    <row r="17" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D16" s="40" t="str">
+        <f>LOOKUP(C16,$A$4:$A$10,$B$4:$B$10)</f>
+        <v>Principal</v>
+      </c>
+      <c r="E16" s="41" t="str">
+        <f>IFERROR(LOOKUP(C16,$A$4:$A$10,$B$4:$B$10),"N/A")</f>
+        <v>Principal</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>31</v>
       </c>
@@ -6409,10 +8036,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A17,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>71000</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="43"/>
-    </row>
-    <row r="18" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D17" s="40" t="str">
+        <f t="shared" ref="D17:D38" si="0">LOOKUP(C17,$A$4:$A$10,$B$4:$B$10)</f>
+        <v>Mid Level</v>
+      </c>
+      <c r="E17" s="41" t="str">
+        <f t="shared" ref="E17:E38" si="1">IFERROR(LOOKUP(C17,$A$4:$A$10,$B$4:$B$10),"N/A")</f>
+        <v>Mid Level</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>35</v>
       </c>
@@ -6424,10 +8057,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A18,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>55000</v>
       </c>
-      <c r="D18" s="40"/>
-      <c r="E18" s="41"/>
-    </row>
-    <row r="19" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Entry Level</v>
+      </c>
+      <c r="E18" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Entry Level</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>38</v>
       </c>
@@ -6439,10 +8078,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A19,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>68000</v>
       </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="43"/>
-    </row>
-    <row r="20" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D19" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Junior</v>
+      </c>
+      <c r="E19" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -6454,10 +8099,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A20,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>95000</v>
       </c>
-      <c r="D20" s="40"/>
-      <c r="E20" s="41"/>
-    </row>
-    <row r="21" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D20" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Principal</v>
+      </c>
+      <c r="E20" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Principal</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>43</v>
       </c>
@@ -6469,10 +8120,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A21,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>58000</v>
       </c>
-      <c r="D21" s="42"/>
-      <c r="E21" s="43"/>
-    </row>
-    <row r="22" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D21" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Entry Level</v>
+      </c>
+      <c r="E21" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Entry Level</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>45</v>
       </c>
@@ -6484,10 +8141,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A22,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>72000</v>
       </c>
-      <c r="D22" s="40"/>
-      <c r="E22" s="41"/>
-    </row>
-    <row r="23" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D22" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Mid Level</v>
+      </c>
+      <c r="E22" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Mid Level</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>47</v>
       </c>
@@ -6499,10 +8162,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A23,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>80000</v>
       </c>
-      <c r="D23" s="42"/>
-      <c r="E23" s="43"/>
-    </row>
-    <row r="24" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D23" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Senior</v>
+      </c>
+      <c r="E23" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Senior</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>49</v>
       </c>
@@ -6514,10 +8183,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A24,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>82000</v>
       </c>
-      <c r="D24" s="40"/>
-      <c r="E24" s="41"/>
-    </row>
-    <row r="25" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D24" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Senior</v>
+      </c>
+      <c r="E24" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Senior</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>51</v>
       </c>
@@ -6529,10 +8204,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A25,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>63000</v>
       </c>
-      <c r="D25" s="42"/>
-      <c r="E25" s="43"/>
-    </row>
-    <row r="26" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D25" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Junior</v>
+      </c>
+      <c r="E25" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>53</v>
       </c>
@@ -6544,10 +8225,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A26,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>60000</v>
       </c>
-      <c r="D26" s="40"/>
-      <c r="E26" s="41"/>
-    </row>
-    <row r="27" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D26" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Junior</v>
+      </c>
+      <c r="E26" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>55</v>
       </c>
@@ -6559,10 +8246,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A27,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>105000</v>
       </c>
-      <c r="D27" s="42"/>
-      <c r="E27" s="43"/>
-    </row>
-    <row r="28" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D27" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Executive</v>
+      </c>
+      <c r="E27" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Executive</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>57</v>
       </c>
@@ -6574,10 +8267,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A28,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>70000</v>
       </c>
-      <c r="D28" s="40"/>
-      <c r="E28" s="41"/>
-    </row>
-    <row r="29" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D28" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Mid Level</v>
+      </c>
+      <c r="E28" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Mid Level</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>59</v>
       </c>
@@ -6589,10 +8288,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A29,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>67000</v>
       </c>
-      <c r="D29" s="42"/>
-      <c r="E29" s="43"/>
-    </row>
-    <row r="30" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D29" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Junior</v>
+      </c>
+      <c r="E29" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>61</v>
       </c>
@@ -6604,10 +8309,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A30,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>58000</v>
       </c>
-      <c r="D30" s="40"/>
-      <c r="E30" s="41"/>
-    </row>
-    <row r="31" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D30" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Entry Level</v>
+      </c>
+      <c r="E30" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Entry Level</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>63</v>
       </c>
@@ -6619,10 +8330,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A31,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>88000</v>
       </c>
-      <c r="D31" s="42"/>
-      <c r="E31" s="43"/>
-    </row>
-    <row r="32" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Senior</v>
+      </c>
+      <c r="E31" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Senior</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>65</v>
       </c>
@@ -6634,10 +8351,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A32,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>76000</v>
       </c>
-      <c r="D32" s="40"/>
-      <c r="E32" s="41"/>
-    </row>
-    <row r="33" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D32" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Mid Level</v>
+      </c>
+      <c r="E32" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Mid Level</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>67</v>
       </c>
@@ -6649,10 +8372,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A33,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>65000</v>
       </c>
-      <c r="D33" s="42"/>
-      <c r="E33" s="43"/>
-    </row>
-    <row r="34" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D33" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Junior</v>
+      </c>
+      <c r="E33" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>69</v>
       </c>
@@ -6664,10 +8393,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A34,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>64000</v>
       </c>
-      <c r="D34" s="40"/>
-      <c r="E34" s="41"/>
-    </row>
-    <row r="35" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D34" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Junior</v>
+      </c>
+      <c r="E34" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>71</v>
       </c>
@@ -6679,10 +8414,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A35,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>79000</v>
       </c>
-      <c r="D35" s="42"/>
-      <c r="E35" s="43"/>
-    </row>
-    <row r="36" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D35" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Mid Level</v>
+      </c>
+      <c r="E35" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Mid Level</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>73</v>
       </c>
@@ -6694,10 +8435,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A36,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>87000</v>
       </c>
-      <c r="D36" s="40"/>
-      <c r="E36" s="41"/>
-    </row>
-    <row r="37" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D36" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Senior</v>
+      </c>
+      <c r="E36" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Senior</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>75</v>
       </c>
@@ -6709,10 +8456,16 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A37,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>61000</v>
       </c>
-      <c r="D37" s="42"/>
-      <c r="E37" s="43"/>
-    </row>
-    <row r="38" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D37" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Junior</v>
+      </c>
+      <c r="E37" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>77</v>
       </c>
@@ -6724,8 +8477,14 @@
         <f>INDEX('Employee Dataset'!$E$4:$E$28, MATCH(A38,'Employee Dataset'!$A$4:$A$28,0))</f>
         <v>73000</v>
       </c>
-      <c r="D38" s="40"/>
-      <c r="E38" s="41"/>
+      <c r="D38" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>Mid Level</v>
+      </c>
+      <c r="E38" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Mid Level</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6754,20 +8513,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>198</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
     </row>
     <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
     </row>
     <row r="4" spans="1:4" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="49" t="s">
@@ -6784,8 +8543,9 @@
       <c r="B5" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="C5" s="52" t="s">
-        <v>203</v>
+      <c r="C5" s="52">
+        <f>VLOOKUP("E007",'Employee Dataset'!A3:L28,MATCH("Salary",'Employee Dataset'!A3:L3,0),FALSE)</f>
+        <v>95000</v>
       </c>
       <c r="D5" s="53" t="s">
         <v>204</v>
@@ -6798,8 +8558,9 @@
       <c r="B6" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="C6" s="52" t="s">
-        <v>203</v>
+      <c r="C6" s="52" t="str">
+        <f>VLOOKUP("E015",'Employee Dataset'!A3:L28,MATCH("Department",'Employee Dataset'!A3:L3,0),FALSE)</f>
+        <v>IT</v>
       </c>
       <c r="D6" s="53" t="s">
         <v>204</v>
@@ -6812,8 +8573,9 @@
       <c r="B7" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="C7" s="52" t="s">
-        <v>203</v>
+      <c r="C7" s="52" t="str">
+        <f>IFERROR(VLOOKUP("E006",'Employee Dataset'!A3:L28,MATCH("Active",'Employee Dataset'!A3:L3,0),FALSE),"Not Found")</f>
+        <v>No</v>
       </c>
       <c r="D7" s="55" t="s">
         <v>209</v>
@@ -6834,9 +8596,7 @@
       <c r="B9" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="C9" s="52" t="s">
-        <v>203</v>
-      </c>
+      <c r="C9" s="52"/>
       <c r="D9" s="55" t="s">
         <v>209</v>
       </c>
